--- a/data/trending_integrated_20260915_11.xlsx
+++ b/data/trending_integrated_20260915_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25600</v>
+        <v>25750</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+16.89%</t>
+          <t>'+17.58%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.01</v>
       </c>
       <c r="E2" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H2" t="n">
         <v>4.9</v>
@@ -610,7 +610,7 @@
         <v>4.89</v>
       </c>
       <c r="O2" t="n">
-        <v>159788573950</v>
+        <v>164925778350</v>
       </c>
       <c r="P2" t="n">
         <v>50600</v>
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10720</v>
+        <v>10770</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.64%</t>
+          <t>'+16.18%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.06</v>
       </c>
       <c r="E3" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F3" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G3" t="n">
         <v>101</v>
@@ -702,7 +702,7 @@
         <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>125050811445</v>
+        <v>125953145415</v>
       </c>
       <c r="P3" t="n">
         <v>25050</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>세계 최초 면역조절 펩타이드 장기지속형 제제 기술 특허 등록. 품절주 및 30만 목표가 제시.</t>
+          <t>싸이모신 알파1 장기지속형 제제 기술 특허 등록. 노보노디스크 협력 및 품절주 특성 강조.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['특허 등록', '품절주', '장기지속형']</t>
+          <t>['특허 등록', '싸이모신 알파1', '품절주']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,70 +747,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>한국첨단소재</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>52000</v>
+        <v>2835</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.79%</t>
+          <t>'+9.67%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.18</v>
+        <v>1.34</v>
       </c>
       <c r="E4" t="n">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="F4" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="G4" t="n">
-        <v>224</v>
+        <v>145</v>
       </c>
       <c r="H4" t="n">
-        <v>13.97</v>
+        <v>1.34</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>47800</v>
+        <v>2585</v>
       </c>
       <c r="K4" t="n">
-        <v>47300</v>
+        <v>2725</v>
       </c>
       <c r="L4" t="n">
-        <v>54600</v>
+        <v>3200</v>
       </c>
       <c r="M4" t="n">
-        <v>46400</v>
+        <v>2690</v>
       </c>
       <c r="N4" t="n">
-        <v>14.15</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>61104413125</v>
+        <v>62786834643</v>
       </c>
       <c r="P4" t="n">
-        <v>108900</v>
+        <v>5100</v>
       </c>
       <c r="Q4" t="n">
-        <v>18230</v>
+        <v>966</v>
       </c>
       <c r="R4" t="n">
-        <v>89000</v>
+        <v>-461000</v>
       </c>
       <c r="S4" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>대형 계약 체결 및 수소법 시행 기대감. 외국인/기관 매도 속 개인 순매수, 경쟁사 주가 상승.</t>
+          <t>미국 기업과 594억 공급 계약 및 세계 최초 타이틀. 트럼프 AI 발언에 따른 기대감 상승.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['수소법', '계약 체결', '연료전지']</t>
+          <t>['공급 계약', 'AI', '세계 최초']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,77 +832,77 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>062970</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>한국첨단소재</t>
+          <t>현대제철</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2805</v>
+        <v>36000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.51%</t>
+          <t>'+9.09%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.34</v>
+        <v>-0.13</v>
       </c>
       <c r="E5" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G5" t="n">
-        <v>147</v>
+        <v>225</v>
       </c>
       <c r="H5" t="n">
-        <v>1.34</v>
+        <v>14.93</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2585</v>
+        <v>33000</v>
       </c>
       <c r="K5" t="n">
-        <v>2725</v>
+        <v>32750</v>
       </c>
       <c r="L5" t="n">
-        <v>3200</v>
+        <v>37200</v>
       </c>
       <c r="M5" t="n">
-        <v>2690</v>
+        <v>32750</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>15.06</v>
       </c>
       <c r="O5" t="n">
-        <v>62292364721</v>
+        <v>39433840200</v>
       </c>
       <c r="P5" t="n">
-        <v>5100</v>
+        <v>50400</v>
       </c>
       <c r="Q5" t="n">
-        <v>966</v>
+        <v>23650</v>
       </c>
       <c r="R5" t="n">
-        <v>-461000</v>
+        <v>318000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>73000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 기업과 594억 공급 계약 및 세계 최초 타이틀. 트럼프 AI 발언에 따른 기대감 상승.</t>
+          <t>저PBR 기업 정책에 따른 상승 기대감. 120일선 돌파 및 정배열 형성.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['공급 계약', 'AI', '세계 최초']</t>
+          <t>['저PBR', '현대제철', '상승']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>062970</t>
+          <t>004020</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>현대제철</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35700</v>
+        <v>52100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.18%</t>
+          <t>'+9.00%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.13</v>
+        <v>-0.18</v>
       </c>
       <c r="E6" t="n">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="G6" t="n">
-        <v>215</v>
+        <v>249</v>
       </c>
       <c r="H6" t="n">
-        <v>14.93</v>
+        <v>13.97</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>33000</v>
+        <v>47800</v>
       </c>
       <c r="K6" t="n">
-        <v>32750</v>
+        <v>47300</v>
       </c>
       <c r="L6" t="n">
-        <v>37200</v>
+        <v>54600</v>
       </c>
       <c r="M6" t="n">
-        <v>32750</v>
+        <v>46400</v>
       </c>
       <c r="N6" t="n">
-        <v>15.06</v>
+        <v>14.15</v>
       </c>
       <c r="O6" t="n">
-        <v>38447973075</v>
+        <v>65199653075</v>
       </c>
       <c r="P6" t="n">
-        <v>50400</v>
+        <v>108900</v>
       </c>
       <c r="Q6" t="n">
-        <v>23650</v>
+        <v>18230</v>
       </c>
       <c r="R6" t="n">
-        <v>318000</v>
+        <v>89000</v>
       </c>
       <c r="S6" t="n">
-        <v>73000</v>
+        <v>21000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>저PBR 기업 정책에 따른 상승 기대감. 120일선 돌파 및 정배열 형성.</t>
+          <t>초대형 계약 체결 공시 확인. 5천억 수주 이력 언급하며 기대감 형성. 다만, 누르려는 움직임 관찰.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['저PBR', '현대제철', '상승']</t>
+          <t>['계약 체결', '수주', '공시']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>004020</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3630</v>
+        <v>3655</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.76%</t>
+          <t>'+7.50%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F7" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="H7" t="n">
         <v>0.83</v>
@@ -1070,7 +1070,7 @@
         <v>0.71</v>
       </c>
       <c r="O7" t="n">
-        <v>134651942226</v>
+        <v>135333809258</v>
       </c>
       <c r="P7" t="n">
         <v>4335</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31900</v>
+        <v>32100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.11%</t>
+          <t>'+5.77%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F8" t="n">
         <v>82</v>
       </c>
       <c r="G8" t="n">
-        <v>541</v>
+        <v>560</v>
       </c>
       <c r="H8" t="n">
         <v>17.5</v>
@@ -1153,7 +1153,7 @@
         <v>30250</v>
       </c>
       <c r="L8" t="n">
-        <v>31900</v>
+        <v>32150</v>
       </c>
       <c r="M8" t="n">
         <v>30250</v>
@@ -1162,7 +1162,7 @@
         <v>17.55</v>
       </c>
       <c r="O8" t="n">
-        <v>7773094475</v>
+        <v>8940096575</v>
       </c>
       <c r="P8" t="n">
         <v>69200</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>담관암 신약 FDA 승인 기대감과 제약 유증 관련 불확실성. 정보 빠른 기관/외인 이탈 관측.</t>
+          <t>담관암 신약 FDA 허가 기대감 속, 기관 외인 이탈 및 제약 유증 이슈. 승인 확률 85~90% 예측.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['담관암', 'FDA 승인', '유증']</t>
+          <t>['담관암 신약', 'FDA 허가', '기관 외인 이탈']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10760</v>
+        <v>14880</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.77%</t>
+          <t>'+5.46%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.26</v>
+        <v>0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>133</v>
+        <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="G9" t="n">
-        <v>333</v>
+        <v>136</v>
       </c>
       <c r="H9" t="n">
-        <v>17.93</v>
+        <v>10.75</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,91 +1239,91 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>10270</v>
+        <v>14110</v>
       </c>
       <c r="K9" t="n">
-        <v>11000</v>
+        <v>14110</v>
       </c>
       <c r="L9" t="n">
-        <v>11650</v>
+        <v>15250</v>
       </c>
       <c r="M9" t="n">
-        <v>10010</v>
+        <v>13400</v>
       </c>
       <c r="N9" t="n">
-        <v>17.67</v>
+        <v>10.69</v>
       </c>
       <c r="O9" t="n">
-        <v>297856007930</v>
+        <v>93126857875</v>
       </c>
       <c r="P9" t="n">
-        <v>22450</v>
+        <v>23550</v>
       </c>
       <c r="Q9" t="n">
-        <v>1760</v>
+        <v>5700</v>
       </c>
       <c r="R9" t="n">
-        <v>276000</v>
+        <v>-68000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>87000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>AI 발전에 따른 광통신 테마 기대감과 아이온큐 급등 소식. 트럼프 관련 발언 및 기타 법인 매수세 확인.</t>
+          <t>거래량 증가와 함께 15000원 돌파 시도, 주포 움직임에 대한 기대와 우려 혼재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['AI', '광통신', '아이온큐']</t>
+          <t>['주포', '거래량', '15000원']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14780</v>
+        <v>10720</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.75%</t>
+          <t>'+4.38%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.06</v>
+        <v>0.26</v>
       </c>
       <c r="E10" t="n">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>93</v>
       </c>
       <c r="G10" t="n">
-        <v>135</v>
+        <v>347</v>
       </c>
       <c r="H10" t="n">
-        <v>10.75</v>
+        <v>17.93</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,60 +1331,60 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14110</v>
+        <v>10270</v>
       </c>
       <c r="K10" t="n">
-        <v>14110</v>
+        <v>11000</v>
       </c>
       <c r="L10" t="n">
-        <v>15250</v>
+        <v>11650</v>
       </c>
       <c r="M10" t="n">
-        <v>13400</v>
+        <v>10010</v>
       </c>
       <c r="N10" t="n">
-        <v>10.69</v>
+        <v>17.67</v>
       </c>
       <c r="O10" t="n">
-        <v>91280075120</v>
+        <v>301358391905</v>
       </c>
       <c r="P10" t="n">
-        <v>23550</v>
+        <v>22450</v>
       </c>
       <c r="Q10" t="n">
-        <v>5700</v>
+        <v>1760</v>
       </c>
       <c r="R10" t="n">
-        <v>-68000</v>
+        <v>276000</v>
       </c>
       <c r="S10" t="n">
-        <v>87000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>거래량 증가와 함께 15000원 돌파 시도, 주포 움직임에 대한 기대와 우려 혼재.</t>
+          <t>아이온큐 급등 및 트럼프 AI 발언에 따른 기대감 형성. 다만, 미국 반도체 지수 하락 및 개인 매도 흐름.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['주포', '거래량', '15000원']</t>
+          <t>['아이온큐', 'AI', '반도체']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>142400</v>
+        <v>142500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+4.17%</t>
+          <t>'+4.24%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F11" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G11" t="n">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="H11" t="n">
         <v>15.81</v>
@@ -1438,7 +1438,7 @@
         <v>15.76</v>
       </c>
       <c r="O11" t="n">
-        <v>81253259650</v>
+        <v>83440312850</v>
       </c>
       <c r="P11" t="n">
         <v>164700</v>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10090</v>
+        <v>19070</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.00%</t>
+          <t>'+1.65%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="F12" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G12" t="n">
-        <v>79</v>
+        <v>228</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6</v>
+        <v>10.53</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>9990</v>
+        <v>18760</v>
       </c>
       <c r="K12" t="n">
-        <v>10110</v>
+        <v>18440</v>
       </c>
       <c r="L12" t="n">
-        <v>11390</v>
+        <v>19070</v>
       </c>
       <c r="M12" t="n">
-        <v>10040</v>
+        <v>18120</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6</v>
+        <v>10.55</v>
       </c>
       <c r="O12" t="n">
-        <v>141861410345</v>
+        <v>38505183515</v>
       </c>
       <c r="P12" t="n">
-        <v>15960</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>3500</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>21000</v>
+        <v>-67000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-18000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>주가 조작 및 공매도 관련 논란, 신약 개발 기대에도 불구하고 하락 압력.</t>
+          <t>대차해지 운동 참여 독려 및 건설 대장주로서의 기대감 표출. 해외 건설 수주 가능성 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['주가 조작', '공매도', '신약']</t>
+          <t>['대차해지', '해외건설', '건설 대장주']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18910</v>
+        <v>10090</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.80%</t>
+          <t>'+1.00%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F13" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="G13" t="n">
-        <v>215</v>
+        <v>80</v>
       </c>
       <c r="H13" t="n">
-        <v>10.53</v>
+        <v>0.6</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>18760</v>
+        <v>9990</v>
       </c>
       <c r="K13" t="n">
-        <v>18440</v>
+        <v>10110</v>
       </c>
       <c r="L13" t="n">
-        <v>19060</v>
+        <v>11390</v>
       </c>
       <c r="M13" t="n">
-        <v>18120</v>
+        <v>10040</v>
       </c>
       <c r="N13" t="n">
-        <v>10.55</v>
+        <v>0.6</v>
       </c>
       <c r="O13" t="n">
-        <v>35658297930</v>
+        <v>142217173480</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>15960</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>3500</v>
       </c>
       <c r="R13" t="n">
-        <v>-67000</v>
+        <v>21000</v>
       </c>
       <c r="S13" t="n">
-        <v>-18000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>대차해지 운동 참여 독려 및 건설 대장주로서의 기대감 표출. 해외 건설 수주 가능성 언급.</t>
+          <t>주가 조작 및 공매도 관련 논란, 신약 개발 기대에도 불구하고 하락 압력.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['대차해지', '해외건설', '건설 대장주']</t>
+          <t>['주가 조작', '공매도', '신약']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1710000</v>
+        <v>1709000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.77%</t>
+          <t>'+0.71%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="G14" t="n">
-        <v>1993</v>
+        <v>2016</v>
       </c>
       <c r="H14" t="n">
         <v>50.27</v>
@@ -1714,7 +1714,7 @@
         <v>50.47</v>
       </c>
       <c r="O14" t="n">
-        <v>1867170090500</v>
+        <v>1942949335000</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>나스닥 선물 흐름 및 외인 매수세 기반 상승 기대감. 조정 끝난 후 반등 가능성 전망.</t>
+          <t>나스닥 선물 흐름 및 시장 반등 기대감. 외국인 매도세 관찰되며, 5만원 돌파 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['나스닥 선물', '외인 매수', '반등']</t>
+          <t>['나스닥 선물', '시장 반등', '외국인']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>226000</v>
+        <v>250250</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+0.44%</t>
+          <t>'+0.50%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.15</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>130</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>69</v>
+        <v>475</v>
       </c>
       <c r="G15" t="n">
-        <v>628</v>
+        <v>1776</v>
       </c>
       <c r="H15" t="n">
-        <v>7.2</v>
+        <v>46.57</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>225000</v>
+        <v>249000</v>
       </c>
       <c r="K15" t="n">
-        <v>228500</v>
+        <v>248000</v>
       </c>
       <c r="L15" t="n">
-        <v>229000</v>
+        <v>252000</v>
       </c>
       <c r="M15" t="n">
-        <v>219500</v>
+        <v>247500</v>
       </c>
       <c r="N15" t="n">
-        <v>7.05</v>
+        <v>46.64</v>
       </c>
       <c r="O15" t="n">
-        <v>64044420750</v>
+        <v>1090941705250</v>
       </c>
       <c r="P15" t="n">
-        <v>426000</v>
+        <v>374500</v>
       </c>
       <c r="Q15" t="n">
-        <v>89500</v>
+        <v>75900</v>
       </c>
       <c r="R15" t="n">
-        <v>-110000</v>
+        <v>-176000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-267000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>머스크 테라팹 공급 관련 단독 뉴스 및 스페이스X 연관 기대감. 공매도 세력과의 대립 구도 형성.</t>
+          <t>메모리 반도체 수요 감소 없음 전망 및 시장 안정화 기대. 정치적 이슈 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['테라팹', '스페이스X', '공매도']</t>
+          <t>['메모리 반도체', '시장 안정화', '악재 선반영']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>106</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>250000</v>
+        <v>226000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.40%</t>
+          <t>'+0.44%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="E16" t="n">
-        <v>800</v>
+        <v>132</v>
       </c>
       <c r="F16" t="n">
-        <v>473</v>
+        <v>69</v>
       </c>
       <c r="G16" t="n">
-        <v>1796</v>
+        <v>645</v>
       </c>
       <c r="H16" t="n">
-        <v>46.57</v>
+        <v>7.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>249000</v>
+        <v>225000</v>
       </c>
       <c r="K16" t="n">
-        <v>248000</v>
+        <v>228500</v>
       </c>
       <c r="L16" t="n">
-        <v>252000</v>
+        <v>229000</v>
       </c>
       <c r="M16" t="n">
-        <v>247500</v>
+        <v>219500</v>
       </c>
       <c r="N16" t="n">
-        <v>46.64</v>
+        <v>7.05</v>
       </c>
       <c r="O16" t="n">
-        <v>1061708824750</v>
+        <v>65278034750</v>
       </c>
       <c r="P16" t="n">
-        <v>374500</v>
+        <v>426000</v>
       </c>
       <c r="Q16" t="n">
-        <v>75900</v>
+        <v>89500</v>
       </c>
       <c r="R16" t="n">
-        <v>-176000</v>
+        <v>-110000</v>
       </c>
       <c r="S16" t="n">
-        <v>-267000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>시장 안정화 기대감 속 삼성전자 반등 가능성 언급. 저가 매수 기회 및 악재 선반영 주장.</t>
+          <t>머스크 테라팹에 패키징 장비 공급 단독 보도. 반도체 반등 및 공매도 세력에 대한 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['시장 안정화', '반등', '저가 매수']</t>
+          <t>['테라팹', '패키징 장비', '공매도']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>106</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6920</v>
+        <v>6930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.29%</t>
+          <t>'+0.43%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1964,7 +1964,7 @@
         <v>27</v>
       </c>
       <c r="G17" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H17" t="n">
         <v>0.7</v>
@@ -1990,7 +1990,7 @@
         <v>1.67</v>
       </c>
       <c r="O17" t="n">
-        <v>29089375935</v>
+        <v>29246318535</v>
       </c>
       <c r="P17" t="n">
         <v>10360</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14650</v>
+        <v>14710</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-0.07%</t>
+          <t>'+0.34%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-1.17</v>
       </c>
       <c r="E18" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F18" t="n">
         <v>79</v>
       </c>
       <c r="G18" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         <v>1.17</v>
       </c>
       <c r="O18" t="n">
-        <v>36817061085</v>
+        <v>37156430365</v>
       </c>
       <c r="P18" t="n">
         <v>36200</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8750</v>
+        <v>8780</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-1.13%</t>
+          <t>'-0.79%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F19" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G19" t="n">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="H19" t="n">
         <v>27.16</v>
@@ -2174,7 +2174,7 @@
         <v>27.16</v>
       </c>
       <c r="O19" t="n">
-        <v>14053560660</v>
+        <v>14307358995</v>
       </c>
       <c r="P19" t="n">
         <v>17950</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>목표주가 하향 조정 및 적자 지속에 대한 부정적 전망. 삼성디스플레이와 비교하며 저평가 주장도 존재.</t>
+          <t>하반기 실적 부진 전망 및 목표가 하향. ADR 폭락 및 적자 지속에 대한 우려.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['목표주가', '적자', 'PBR']</t>
+          <t>['실적 부진', '목표가 하향', 'ADR']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>85500</v>
+        <v>86000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-1.72%</t>
+          <t>'-1.15%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.11</v>
       </c>
       <c r="E20" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F20" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G20" t="n">
-        <v>628</v>
+        <v>641</v>
       </c>
       <c r="H20" t="n">
         <v>23.45</v>
@@ -2266,7 +2266,7 @@
         <v>23.56</v>
       </c>
       <c r="O20" t="n">
-        <v>73287084450</v>
+        <v>76348386850</v>
       </c>
       <c r="P20" t="n">
         <v>139200</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14235</v>
+        <v>14250</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-1.76%</t>
+          <t>'-1.66%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.08</v>
       </c>
       <c r="E21" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F21" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G21" t="n">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="H21" t="n">
         <v>1.8</v>
@@ -2358,7 +2358,7 @@
         <v>1.88</v>
       </c>
       <c r="O21" t="n">
-        <v>42711426600</v>
+        <v>43496197330</v>
       </c>
       <c r="P21" t="n">
         <v>31500</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4190</v>
+        <v>4195</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-3.12%</t>
+          <t>'-3.01%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.18</v>
       </c>
       <c r="E22" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F22" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G22" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="H22" t="n">
         <v>0.77</v>
@@ -2450,7 +2450,7 @@
         <v>0.59</v>
       </c>
       <c r="O22" t="n">
-        <v>57144928797</v>
+        <v>58073668457</v>
       </c>
       <c r="P22" t="n">
         <v>8100</v>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>21100</v>
+        <v>21150</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-4.52%</t>
+          <t>'-4.30%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.09</v>
       </c>
       <c r="E23" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F23" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G23" t="n">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="H23" t="n">
         <v>28.9</v>
@@ -2542,7 +2542,7 @@
         <v>28.81</v>
       </c>
       <c r="O23" t="n">
-        <v>39309050225</v>
+        <v>40730678075</v>
       </c>
       <c r="P23" t="n">
         <v>35350</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>12억 달러 수주 공시에도 불구하고 주가 하락. 시장의 수주 악재 해석 및 투자자 불만 제기.</t>
+          <t>12억 달러 수주 공시 확인. 그러나 주가는 하락세이며, 수급 및 기업 주포에 대한 부정적 언급.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['수주 공시', '주가 하락', '조선주']</t>
+          <t>['수주 공시', '주가 하락', '수급']</t>
         </is>
       </c>
       <c r="X23" t="n">

--- a/data/trending_integrated_20260915_11.xlsx
+++ b/data/trending_integrated_20260915_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25750</v>
+        <v>25700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+17.58%</t>
+          <t>'+17.35%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.01</v>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="F2" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G2" t="n">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="H2" t="n">
         <v>4.9</v>
@@ -610,7 +610,7 @@
         <v>4.89</v>
       </c>
       <c r="O2" t="n">
-        <v>164925778350</v>
+        <v>168350269700</v>
       </c>
       <c r="P2" t="n">
         <v>50600</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10770</v>
+        <v>10780</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.18%</t>
+          <t>'+16.29%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.06</v>
       </c>
       <c r="E3" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F3" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G3" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="H3" t="n">
         <v>1.19</v>
@@ -702,7 +702,7 @@
         <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>125953145415</v>
+        <v>127149539570</v>
       </c>
       <c r="P3" t="n">
         <v>25050</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>싸이모신 알파1 장기지속형 제제 기술 특허 등록. 노보노디스크 협력 및 품절주 특성 강조.</t>
+          <t>싸이모신 알파1 장기지속형 제제 기술 특허 등록. 세계 최초 기술 기반 품절주로서 높은 상승 기대. 노보노디스크 협력 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['특허 등록', '싸이모신 알파1', '품절주']</t>
+          <t>['싸이모신 알파1', '펩타이드', '품절주']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2835</v>
+        <v>2830</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+9.67%</t>
+          <t>'+9.48%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>1.34</v>
       </c>
       <c r="E4" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H4" t="n">
         <v>1.34</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>62786834643</v>
+        <v>63200961888</v>
       </c>
       <c r="P4" t="n">
         <v>5100</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36000</v>
+        <v>35900</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.09%</t>
+          <t>'+8.79%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.13</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G5" t="n">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="H5" t="n">
         <v>14.93</v>
@@ -886,7 +886,7 @@
         <v>15.06</v>
       </c>
       <c r="O5" t="n">
-        <v>39433840200</v>
+        <v>40191253625</v>
       </c>
       <c r="P5" t="n">
         <v>50400</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52100</v>
+        <v>51600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.00%</t>
+          <t>'+7.95%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.18</v>
       </c>
       <c r="E6" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="F6" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G6" t="n">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="H6" t="n">
         <v>13.97</v>
@@ -978,7 +978,7 @@
         <v>14.15</v>
       </c>
       <c r="O6" t="n">
-        <v>65199653075</v>
+        <v>67491683975</v>
       </c>
       <c r="P6" t="n">
         <v>108900</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>초대형 계약 체결 공시 확인. 5천억 수주 이력 언급하며 기대감 형성. 다만, 누르려는 움직임 관찰.</t>
+          <t>초대형 계약 체결 공시로 인한 기대감 상승. 수주 물량 확보 및 향후 생산 능력 증대 전망. 다만, 이전 수주 이력 대비 주가 반응은 미미.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['계약 체결', '수주', '공시']</t>
+          <t>['계약 체결', '수주', '캐파']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3655</v>
+        <v>3640</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.50%</t>
+          <t>'+7.06%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F7" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G7" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="H7" t="n">
         <v>0.83</v>
@@ -1070,7 +1070,7 @@
         <v>0.71</v>
       </c>
       <c r="O7" t="n">
-        <v>135333809258</v>
+        <v>136191672189</v>
       </c>
       <c r="P7" t="n">
         <v>4335</v>
@@ -1115,79 +1115,79 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32100</v>
+        <v>14940</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.77%</t>
+          <t>'+5.88%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>122</v>
+        <v>51</v>
       </c>
       <c r="F8" t="n">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="G8" t="n">
-        <v>560</v>
+        <v>143</v>
       </c>
       <c r="H8" t="n">
-        <v>17.5</v>
+        <v>10.75</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>30350</v>
+        <v>14110</v>
       </c>
       <c r="K8" t="n">
-        <v>30250</v>
+        <v>14110</v>
       </c>
       <c r="L8" t="n">
-        <v>32150</v>
+        <v>15250</v>
       </c>
       <c r="M8" t="n">
-        <v>30250</v>
+        <v>13400</v>
       </c>
       <c r="N8" t="n">
-        <v>17.55</v>
+        <v>10.69</v>
       </c>
       <c r="O8" t="n">
-        <v>8940096575</v>
+        <v>95847082085</v>
       </c>
       <c r="P8" t="n">
-        <v>69200</v>
+        <v>23550</v>
       </c>
       <c r="Q8" t="n">
-        <v>24150</v>
+        <v>5700</v>
       </c>
       <c r="R8" t="n">
-        <v>25000</v>
+        <v>-68000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>87000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>담관암 신약 FDA 허가 기대감 속, 기관 외인 이탈 및 제약 유증 이슈. 승인 확률 85~90% 예측.</t>
+          <t>거래량 증가와 함께 15000원 돌파 시도, 주포 움직임에 대한 기대와 우려 혼재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['담관암 신약', 'FDA 허가', '기관 외인 이탈']</t>
+          <t>['주포', '거래량', '15000원']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,91 +1195,91 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14880</v>
+        <v>32000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.46%</t>
+          <t>'+5.44%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>49</v>
+        <v>129</v>
       </c>
       <c r="F9" t="n">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="G9" t="n">
-        <v>136</v>
+        <v>587</v>
       </c>
       <c r="H9" t="n">
-        <v>10.75</v>
+        <v>17.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14110</v>
+        <v>30350</v>
       </c>
       <c r="K9" t="n">
-        <v>14110</v>
+        <v>30250</v>
       </c>
       <c r="L9" t="n">
-        <v>15250</v>
+        <v>32300</v>
       </c>
       <c r="M9" t="n">
-        <v>13400</v>
+        <v>30250</v>
       </c>
       <c r="N9" t="n">
-        <v>10.69</v>
+        <v>17.55</v>
       </c>
       <c r="O9" t="n">
-        <v>93126857875</v>
+        <v>9685428925</v>
       </c>
       <c r="P9" t="n">
-        <v>23550</v>
+        <v>69200</v>
       </c>
       <c r="Q9" t="n">
-        <v>5700</v>
+        <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>-68000</v>
+        <v>25000</v>
       </c>
       <c r="S9" t="n">
-        <v>87000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>거래량 증가와 함께 15000원 돌파 시도, 주포 움직임에 대한 기대와 우려 혼재.</t>
+          <t>담관암 신약 FDA 허가 기대감 속, 기관 외인 이탈 및 제약 유증 이슈. 승인 확률 85~90% 예측.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['주포', '거래량', '15000원']</t>
+          <t>['담관암 신약', 'FDA 허가', '기관 외인 이탈']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,43 +1287,43 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10720</v>
+        <v>142900</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.38%</t>
+          <t>'+4.54%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.26</v>
+        <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="F10" t="n">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="G10" t="n">
-        <v>347</v>
+        <v>263</v>
       </c>
       <c r="H10" t="n">
-        <v>17.93</v>
+        <v>15.81</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,38 +1331,38 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>10270</v>
+        <v>136700</v>
       </c>
       <c r="K10" t="n">
-        <v>11000</v>
+        <v>139500</v>
       </c>
       <c r="L10" t="n">
-        <v>11650</v>
+        <v>144100</v>
       </c>
       <c r="M10" t="n">
-        <v>10010</v>
+        <v>138200</v>
       </c>
       <c r="N10" t="n">
-        <v>17.67</v>
+        <v>15.76</v>
       </c>
       <c r="O10" t="n">
-        <v>301358391905</v>
+        <v>85320713400</v>
       </c>
       <c r="P10" t="n">
-        <v>22450</v>
+        <v>164700</v>
       </c>
       <c r="Q10" t="n">
-        <v>1760</v>
+        <v>87700</v>
       </c>
       <c r="R10" t="n">
-        <v>276000</v>
+        <v>7000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>아이온큐 급등 및 트럼프 AI 발언에 따른 기대감 형성. 다만, 미국 반도체 지수 하락 및 개인 매도 흐름.</t>
+          <t>합병 철회 가능성 및 주주 반대 움직임. 영업이익 10조 전망에도 불구하고, 합병 이슈 및 수급 불안으로 인한 주가 변동성.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['아이온큐', 'AI', '반도체']</t>
+          <t>['합병', '주주총회', '영업이익']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>142500</v>
+        <v>10680</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+4.24%</t>
+          <t>'+3.99%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.05</v>
+        <v>0.26</v>
       </c>
       <c r="E11" t="n">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="F11" t="n">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>263</v>
+        <v>362</v>
       </c>
       <c r="H11" t="n">
-        <v>15.81</v>
+        <v>17.93</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>136700</v>
+        <v>10270</v>
       </c>
       <c r="K11" t="n">
-        <v>139500</v>
+        <v>11000</v>
       </c>
       <c r="L11" t="n">
-        <v>144100</v>
+        <v>11650</v>
       </c>
       <c r="M11" t="n">
-        <v>138200</v>
+        <v>10010</v>
       </c>
       <c r="N11" t="n">
-        <v>15.76</v>
+        <v>17.67</v>
       </c>
       <c r="O11" t="n">
-        <v>83440312850</v>
+        <v>304921572660</v>
       </c>
       <c r="P11" t="n">
-        <v>164700</v>
+        <v>22450</v>
       </c>
       <c r="Q11" t="n">
-        <v>87700</v>
+        <v>1760</v>
       </c>
       <c r="R11" t="n">
-        <v>7000</v>
+        <v>276000</v>
       </c>
       <c r="S11" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>합병 관련 불확실성 및 정유/배터리 사업 기대감. 주가 하락 및 상승 가능성에 대한 상반된 의견.</t>
+          <t>한국첨단소재와 연계된 광통신 테마 상승 기대. 아이온큐 급등 영향으로 인한 긍정적 전망. 다만, 트럼프 AI 정책 관련 불확실성 존재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['합병', '정유', '배터리']</t>
+          <t>['광통신', '아이온큐', 'AI']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19070</v>
+        <v>19140</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.65%</t>
+          <t>'+2.03%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G12" t="n">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="H12" t="n">
         <v>10.53</v>
@@ -1521,7 +1521,7 @@
         <v>18440</v>
       </c>
       <c r="L12" t="n">
-        <v>19070</v>
+        <v>19150</v>
       </c>
       <c r="M12" t="n">
         <v>18120</v>
@@ -1530,7 +1530,7 @@
         <v>10.55</v>
       </c>
       <c r="O12" t="n">
-        <v>38505183515</v>
+        <v>41534117100</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10090</v>
+        <v>10080</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.00%</t>
+          <t>'+0.90%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F13" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G13" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H13" t="n">
         <v>0.6</v>
@@ -1622,7 +1622,7 @@
         <v>0.6</v>
       </c>
       <c r="O13" t="n">
-        <v>142217173480</v>
+        <v>143069056130</v>
       </c>
       <c r="P13" t="n">
         <v>15960</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1709000</v>
+        <v>1710000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.71%</t>
+          <t>'+0.77%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G14" t="n">
-        <v>2016</v>
+        <v>2062</v>
       </c>
       <c r="H14" t="n">
         <v>50.27</v>
@@ -1714,7 +1714,7 @@
         <v>50.47</v>
       </c>
       <c r="O14" t="n">
-        <v>1942949335000</v>
+        <v>2016509800500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>나스닥 선물 흐름 및 시장 반등 기대감. 외국인 매도세 관찰되며, 5만원 돌파 전망.</t>
+          <t>나스닥 및 코스피 야간 선물 흐름 긍정적, 조정 마무리 후 반등 기대. 외국인 매수세 유입 시 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['나스닥 선물', '시장 반등', '외국인']</t>
+          <t>['나스닥', '조정', '반등']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>250250</v>
+        <v>226000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+0.50%</t>
+          <t>'+0.44%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>135</v>
       </c>
       <c r="F15" t="n">
-        <v>475</v>
+        <v>70</v>
       </c>
       <c r="G15" t="n">
-        <v>1776</v>
+        <v>709</v>
       </c>
       <c r="H15" t="n">
-        <v>46.57</v>
+        <v>7.2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>249000</v>
+        <v>225000</v>
       </c>
       <c r="K15" t="n">
-        <v>248000</v>
+        <v>228500</v>
       </c>
       <c r="L15" t="n">
-        <v>252000</v>
+        <v>229000</v>
       </c>
       <c r="M15" t="n">
-        <v>247500</v>
+        <v>219500</v>
       </c>
       <c r="N15" t="n">
-        <v>46.64</v>
+        <v>7.05</v>
       </c>
       <c r="O15" t="n">
-        <v>1090941705250</v>
+        <v>65667317500</v>
       </c>
       <c r="P15" t="n">
-        <v>374500</v>
+        <v>426000</v>
       </c>
       <c r="Q15" t="n">
-        <v>75900</v>
+        <v>89500</v>
       </c>
       <c r="R15" t="n">
-        <v>-176000</v>
+        <v>-110000</v>
       </c>
       <c r="S15" t="n">
-        <v>-267000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>메모리 반도체 수요 감소 없음 전망 및 시장 안정화 기대. 정치적 이슈 언급.</t>
+          <t>머스크 테슬라 테라팹 공급 계약 뉴스 부각. 패키징 장비 시장 경쟁력 강화 및 우주 섹터 연계 기대. 공매도 세력과의 공방전 예상.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['메모리 반도체', '시장 안정화', '악재 선반영']</t>
+          <t>['테라팹', '패키징 장비', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>106</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>226000</v>
+        <v>250000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.44%</t>
+          <t>'+0.40%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.15</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>132</v>
+        <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>69</v>
+        <v>482</v>
       </c>
       <c r="G16" t="n">
-        <v>645</v>
+        <v>1784</v>
       </c>
       <c r="H16" t="n">
-        <v>7.2</v>
+        <v>46.57</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>225000</v>
+        <v>249000</v>
       </c>
       <c r="K16" t="n">
-        <v>228500</v>
+        <v>248000</v>
       </c>
       <c r="L16" t="n">
-        <v>229000</v>
+        <v>252000</v>
       </c>
       <c r="M16" t="n">
-        <v>219500</v>
+        <v>247500</v>
       </c>
       <c r="N16" t="n">
-        <v>7.05</v>
+        <v>46.64</v>
       </c>
       <c r="O16" t="n">
-        <v>65278034750</v>
+        <v>1128756496250</v>
       </c>
       <c r="P16" t="n">
-        <v>426000</v>
+        <v>374500</v>
       </c>
       <c r="Q16" t="n">
-        <v>89500</v>
+        <v>75900</v>
       </c>
       <c r="R16" t="n">
-        <v>-110000</v>
+        <v>-176000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-267000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>머스크 테라팹에 패키징 장비 공급 단독 보도. 반도체 반등 및 공매도 세력에 대한 언급.</t>
+          <t>반도체 시장 안정화 및 수요 감소 없음 전망. 저가 매수 기회 언급, 차트 긍정적 분석.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['테라팹', '패키징 장비', '공매도']</t>
+          <t>['메모리 반도체', '수요', '저가 매수']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>106</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6930</v>
+        <v>14680</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.43%</t>
+          <t>'+0.14%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.97</v>
+        <v>-1.17</v>
       </c>
       <c r="E17" t="n">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="F17" t="n">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="G17" t="n">
-        <v>97</v>
+        <v>294</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,91 +1975,91 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>6900</v>
+        <v>14660</v>
       </c>
       <c r="K17" t="n">
-        <v>7500</v>
+        <v>14980</v>
       </c>
       <c r="L17" t="n">
-        <v>8190</v>
+        <v>15460</v>
       </c>
       <c r="M17" t="n">
-        <v>6730</v>
+        <v>14330</v>
       </c>
       <c r="N17" t="n">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="O17" t="n">
-        <v>29246318535</v>
+        <v>37685520305</v>
       </c>
       <c r="P17" t="n">
-        <v>10360</v>
+        <v>36200</v>
       </c>
       <c r="Q17" t="n">
-        <v>2965</v>
+        <v>8920</v>
       </c>
       <c r="R17" t="n">
-        <v>61000</v>
+        <v>-7000</v>
       </c>
       <c r="S17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
+          <t>이란-미국 관계 완화 및 국제유가 상승 기대감. 후티 반군 공격 및 중국 원유 매집으로 인한 유가 변동성 증폭. 다만, 주가 반응은 미미.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['사이버보안', '양자암호', '공급계약']</t>
+          <t>['국제유가', '이란', 'WTI']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14710</v>
+        <v>6900</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.34%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-1.17</v>
+        <v>-0.97</v>
       </c>
       <c r="E18" t="n">
-        <v>125</v>
+        <v>42</v>
       </c>
       <c r="F18" t="n">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="G18" t="n">
-        <v>292</v>
+        <v>101</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,60 +2067,60 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>14660</v>
+        <v>6900</v>
       </c>
       <c r="K18" t="n">
-        <v>14980</v>
+        <v>7500</v>
       </c>
       <c r="L18" t="n">
-        <v>15460</v>
+        <v>8190</v>
       </c>
       <c r="M18" t="n">
-        <v>14330</v>
+        <v>6730</v>
       </c>
       <c r="N18" t="n">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="O18" t="n">
-        <v>37156430365</v>
+        <v>29440097570</v>
       </c>
       <c r="P18" t="n">
-        <v>36200</v>
+        <v>10360</v>
       </c>
       <c r="Q18" t="n">
-        <v>8920</v>
+        <v>2965</v>
       </c>
       <c r="R18" t="n">
-        <v>-7000</v>
+        <v>61000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>이란 관련 지정학적 리스크 및 국제유가 상승 기대감. 유가 변동성에 따른 주가 흐름 전망.</t>
+          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['국제유가', '이란', '지정학적 리스크']</t>
+          <t>['사이버보안', '양자암호', '공급계약']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8780</v>
+        <v>8790</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-0.79%</t>
+          <t>'-0.68%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F19" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G19" t="n">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="H19" t="n">
         <v>27.16</v>
@@ -2174,7 +2174,7 @@
         <v>27.16</v>
       </c>
       <c r="O19" t="n">
-        <v>14307358995</v>
+        <v>14628205690</v>
       </c>
       <c r="P19" t="n">
         <v>17950</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>하반기 실적 부진 전망 및 목표가 하향. ADR 폭락 및 적자 지속에 대한 우려.</t>
+          <t>하반기 실적 부진 및 목표주가 하향 전망. PBR 기반 저평가 주장과 공매도 이슈 혼재.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['실적 부진', '목표가 하향', 'ADR']</t>
+          <t>['실적 부진', '목표주가', '공매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>86000</v>
+        <v>86100</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-1.15%</t>
+          <t>'-1.03%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.11</v>
       </c>
       <c r="E20" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F20" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G20" t="n">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="H20" t="n">
         <v>23.45</v>
@@ -2266,7 +2266,7 @@
         <v>23.56</v>
       </c>
       <c r="O20" t="n">
-        <v>76348386850</v>
+        <v>78963379200</v>
       </c>
       <c r="P20" t="n">
         <v>139200</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14250</v>
+        <v>14270</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-1.66%</t>
+          <t>'-1.52%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.08</v>
       </c>
       <c r="E21" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="F21" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G21" t="n">
-        <v>368</v>
+        <v>391</v>
       </c>
       <c r="H21" t="n">
         <v>1.8</v>
@@ -2358,7 +2358,7 @@
         <v>1.88</v>
       </c>
       <c r="O21" t="n">
-        <v>43496197330</v>
+        <v>43869429665</v>
       </c>
       <c r="P21" t="n">
         <v>31500</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>머니투데이 방송 언급 및 외인 매수 전환 등 긍정적 신호가 있으나, 금일 주가는 부진하며 불확실성이 존재함.</t>
+          <t>방송 홍보 효과와 외인 매수 전환에 대한 기대감, 그러나 금리 및 유가 등 거시 경제 변수로 인한 시장 변동성 우려.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['머니투데이', '외인 매수', '광통신']</t>
+          <t>['외인매수', '대선변수', '금리']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4195</v>
+        <v>4225</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-3.01%</t>
+          <t>'-2.31%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.18</v>
       </c>
       <c r="E22" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F22" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G22" t="n">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="H22" t="n">
         <v>0.77</v>
@@ -2450,7 +2450,7 @@
         <v>0.59</v>
       </c>
       <c r="O22" t="n">
-        <v>58073668457</v>
+        <v>59178590195</v>
       </c>
       <c r="P22" t="n">
         <v>8100</v>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>21150</v>
+        <v>21100</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-4.30%</t>
+          <t>'-4.52%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.09</v>
       </c>
       <c r="E23" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F23" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G23" t="n">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="H23" t="n">
         <v>28.9</v>
@@ -2542,7 +2542,7 @@
         <v>28.81</v>
       </c>
       <c r="O23" t="n">
-        <v>40730678075</v>
+        <v>41781370525</v>
       </c>
       <c r="P23" t="n">
         <v>35350</v>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>12억 달러 수주 공시 확인. 그러나 주가는 하락세이며, 수급 및 기업 주포에 대한 부정적 언급.</t>
+          <t>12억 달러 규모 수주 공시 확인. 조선업황 회복 기대감 있으나, 시장 반응 및 수급 악화로 인한 주가 하락.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['수주 공시', '주가 하락', '수급']</t>
+          <t>['수주 공시', '조선업황', '수급']</t>
         </is>
       </c>
       <c r="X23" t="n">

--- a/data/trending_integrated_20260915_11.xlsx
+++ b/data/trending_integrated_20260915_11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z23"/>
+  <dimension ref="A1:Z24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25700</v>
+        <v>25550</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+17.35%</t>
+          <t>'+16.67%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.01</v>
       </c>
       <c r="E2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G2" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="H2" t="n">
         <v>4.9</v>
@@ -610,7 +610,7 @@
         <v>4.89</v>
       </c>
       <c r="O2" t="n">
-        <v>168350269700</v>
+        <v>172146884600</v>
       </c>
       <c r="P2" t="n">
         <v>50600</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10780</v>
+        <v>10610</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.29%</t>
+          <t>'+14.46%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.06</v>
       </c>
       <c r="E3" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H3" t="n">
         <v>1.19</v>
@@ -702,7 +702,7 @@
         <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>127149539570</v>
+        <v>129426305695</v>
       </c>
       <c r="P3" t="n">
         <v>25050</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>싸이모신 알파1 장기지속형 제제 기술 특허 등록. 세계 최초 기술 기반 품절주로서 높은 상승 기대. 노보노디스크 협력 가능성 언급.</t>
+          <t>면역조절 펩타이드 장기지속형 제제 기술 특허 등록 및 관련 기대감. 품절주 특성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['싸이모신 알파1', '펩타이드', '품절주']</t>
+          <t>['특허', '펩타이드', '품절주']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2830</v>
+        <v>2855</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+9.48%</t>
+          <t>'+10.44%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>1.34</v>
       </c>
       <c r="E4" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G4" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H4" t="n">
         <v>1.34</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>63200961888</v>
+        <v>63687918114</v>
       </c>
       <c r="P4" t="n">
         <v>5100</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35900</v>
+        <v>35800</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.79%</t>
+          <t>'+8.48%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.13</v>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G5" t="n">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H5" t="n">
         <v>14.93</v>
@@ -886,7 +886,7 @@
         <v>15.06</v>
       </c>
       <c r="O5" t="n">
-        <v>40191253625</v>
+        <v>40811654875</v>
       </c>
       <c r="P5" t="n">
         <v>50400</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51600</v>
+        <v>51100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.95%</t>
+          <t>'+6.90%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.18</v>
       </c>
       <c r="E6" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="F6" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G6" t="n">
-        <v>290</v>
+        <v>317</v>
       </c>
       <c r="H6" t="n">
         <v>13.97</v>
@@ -978,7 +978,7 @@
         <v>14.15</v>
       </c>
       <c r="O6" t="n">
-        <v>67491683975</v>
+        <v>71023318525</v>
       </c>
       <c r="P6" t="n">
         <v>108900</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>초대형 계약 체결 공시로 인한 기대감 상승. 수주 물량 확보 및 향후 생산 능력 증대 전망. 다만, 이전 수주 이력 대비 주가 반응은 미미.</t>
+          <t>초대형 계약 체결 가능성 및 수주 성과에 따른 기대감. 외인, 보험, 투신, 연기금 등 기관 매수세 유입 확인.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['계약 체결', '수주', '캐파']</t>
+          <t>['수주', '계약체결', '기관매수']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3640</v>
+        <v>3625</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.06%</t>
+          <t>'+6.62%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G7" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H7" t="n">
         <v>0.83</v>
@@ -1070,7 +1070,7 @@
         <v>0.71</v>
       </c>
       <c r="O7" t="n">
-        <v>136191672189</v>
+        <v>137649268614</v>
       </c>
       <c r="P7" t="n">
         <v>4335</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14940</v>
+        <v>14880</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.88%</t>
+          <t>'+5.46%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F8" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G8" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H8" t="n">
         <v>10.75</v>
@@ -1162,7 +1162,7 @@
         <v>10.69</v>
       </c>
       <c r="O8" t="n">
-        <v>95847082085</v>
+        <v>96839142060</v>
       </c>
       <c r="P8" t="n">
         <v>23550</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32000</v>
+        <v>31950</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.44%</t>
+          <t>'+5.27%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F9" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G9" t="n">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="H9" t="n">
         <v>17.5</v>
@@ -1254,7 +1254,7 @@
         <v>17.55</v>
       </c>
       <c r="O9" t="n">
-        <v>9685428925</v>
+        <v>10155821975</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>142900</v>
+        <v>143200</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.54%</t>
+          <t>'+4.75%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>66</v>
       </c>
       <c r="G10" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="H10" t="n">
         <v>15.81</v>
@@ -1346,7 +1346,7 @@
         <v>15.76</v>
       </c>
       <c r="O10" t="n">
-        <v>85320713400</v>
+        <v>87423984400</v>
       </c>
       <c r="P10" t="n">
         <v>164700</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>합병 철회 가능성 및 주주 반대 움직임. 영업이익 10조 전망에도 불구하고, 합병 이슈 및 수급 불안으로 인한 주가 변동성.</t>
+          <t>합병 철회 가능성 및 적자 회사 합병 관련 우려 제기. 주주총회 합병 반대 촉구.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['합병', '주주총회', '영업이익']</t>
+          <t>['합병', '적자', '주주총회']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10680</v>
+        <v>10710</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.99%</t>
+          <t>'+4.28%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.26</v>
       </c>
       <c r="E11" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F11" t="n">
         <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="H11" t="n">
         <v>17.93</v>
@@ -1438,7 +1438,7 @@
         <v>17.67</v>
       </c>
       <c r="O11" t="n">
-        <v>304921572660</v>
+        <v>309293641455</v>
       </c>
       <c r="P11" t="n">
         <v>22450</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>한국첨단소재와 연계된 광통신 테마 상승 기대. 아이온큐 급등 영향으로 인한 긍정적 전망. 다만, 트럼프 AI 정책 관련 불확실성 존재.</t>
+          <t>아이온큐 급등 및 트럼프 AI 발언에 따른 기대감 형성. 다만, 미국 반도체 지수 하락 및 개인 매도 흐름.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', '아이온큐', 'AI']</t>
+          <t>['아이온큐', 'AI', '반도체']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,123 +1483,123 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19140</v>
+        <v>17740</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.03%</t>
+          <t>'+3.14%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.02</v>
+        <v>-2.35</v>
       </c>
       <c r="E12" t="n">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="G12" t="n">
-        <v>244</v>
+        <v>140</v>
       </c>
       <c r="H12" t="n">
-        <v>10.53</v>
+        <v>0.35</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>18760</v>
+        <v>17200</v>
       </c>
       <c r="K12" t="n">
-        <v>18440</v>
+        <v>17220</v>
       </c>
       <c r="L12" t="n">
-        <v>19150</v>
+        <v>18390</v>
       </c>
       <c r="M12" t="n">
-        <v>18120</v>
+        <v>16600</v>
       </c>
       <c r="N12" t="n">
-        <v>10.55</v>
+        <v>2.7</v>
       </c>
       <c r="O12" t="n">
-        <v>41534117100</v>
+        <v>133520180025</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>30550</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>6100</v>
       </c>
       <c r="R12" t="n">
-        <v>-67000</v>
+        <v>149000</v>
       </c>
       <c r="S12" t="n">
-        <v>-18000</v>
+        <v>4000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>대차해지 운동 참여 독려 및 건설 대장주로서의 기대감 표출. 해외 건설 수주 가능성 언급.</t>
+          <t>미국 양자 보안주 폭등 및 세계 최초 기술력 기반 공급 계약 체결 사실. 관련 기업 비교.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['대차해지', '해외건설', '건설 대장주']</t>
+          <t>['양자보안', '공급계약', '기술력']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10080</v>
+        <v>19230</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.90%</t>
+          <t>'+2.51%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="F13" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G13" t="n">
-        <v>83</v>
+        <v>260</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6</v>
+        <v>10.53</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>9990</v>
+        <v>18760</v>
       </c>
       <c r="K13" t="n">
-        <v>10110</v>
+        <v>18440</v>
       </c>
       <c r="L13" t="n">
-        <v>11390</v>
+        <v>19230</v>
       </c>
       <c r="M13" t="n">
-        <v>10040</v>
+        <v>18120</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6</v>
+        <v>10.55</v>
       </c>
       <c r="O13" t="n">
-        <v>143069056130</v>
+        <v>43754574395</v>
       </c>
       <c r="P13" t="n">
-        <v>15960</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>3500</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>21000</v>
+        <v>-67000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-18000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>주가 조작 및 공매도 관련 논란, 신약 개발 기대에도 불구하고 하락 압력.</t>
+          <t>대차해지 운동 참여 독려 및 건설 대장주로서의 기대감 표출. 해외 건설 수주 가능성 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주가 조작', '공매도', '신약']</t>
+          <t>['대차해지', '해외건설', '건설 대장주']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,130 +1660,130 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1710000</v>
+        <v>7050</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.77%</t>
+          <t>'+2.17%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.2</v>
+        <v>-0.97</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>42</v>
       </c>
       <c r="F14" t="n">
-        <v>460</v>
+        <v>27</v>
       </c>
       <c r="G14" t="n">
-        <v>2062</v>
+        <v>101</v>
       </c>
       <c r="H14" t="n">
-        <v>50.27</v>
+        <v>0.7</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1697000</v>
+        <v>6900</v>
       </c>
       <c r="K14" t="n">
-        <v>1690000</v>
+        <v>7500</v>
       </c>
       <c r="L14" t="n">
-        <v>1725000</v>
+        <v>8190</v>
       </c>
       <c r="M14" t="n">
-        <v>1685000</v>
+        <v>6730</v>
       </c>
       <c r="N14" t="n">
-        <v>50.47</v>
+        <v>1.67</v>
       </c>
       <c r="O14" t="n">
-        <v>2016509800500</v>
+        <v>30605731480</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>10360</v>
       </c>
       <c r="Q14" t="n">
-        <v>325000</v>
+        <v>2965</v>
       </c>
       <c r="R14" t="n">
-        <v>-118000</v>
+        <v>61000</v>
       </c>
       <c r="S14" t="n">
-        <v>-48000</v>
+        <v>1000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>나스닥 및 코스피 야간 선물 흐름 긍정적, 조정 마무리 후 반등 기대. 외국인 매수세 유입 시 상승 가능성 언급.</t>
+          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['나스닥', '조정', '반등']</t>
+          <t>['사이버보안', '양자암호', '공급계약']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>226000</v>
+        <v>1718000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+0.44%</t>
+          <t>'+1.24%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.15</v>
+        <v>-0.2</v>
       </c>
       <c r="E15" t="n">
-        <v>135</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>70</v>
+        <v>463</v>
       </c>
       <c r="G15" t="n">
-        <v>709</v>
+        <v>2099</v>
       </c>
       <c r="H15" t="n">
-        <v>7.2</v>
+        <v>50.27</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>225000</v>
+        <v>1697000</v>
       </c>
       <c r="K15" t="n">
-        <v>228500</v>
+        <v>1690000</v>
       </c>
       <c r="L15" t="n">
-        <v>229000</v>
+        <v>1725000</v>
       </c>
       <c r="M15" t="n">
-        <v>219500</v>
+        <v>1685000</v>
       </c>
       <c r="N15" t="n">
-        <v>7.05</v>
+        <v>50.47</v>
       </c>
       <c r="O15" t="n">
-        <v>65667317500</v>
+        <v>2098326632500</v>
       </c>
       <c r="P15" t="n">
-        <v>426000</v>
+        <v>2987000</v>
       </c>
       <c r="Q15" t="n">
-        <v>89500</v>
+        <v>325000</v>
       </c>
       <c r="R15" t="n">
-        <v>-110000</v>
+        <v>-118000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-48000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>머스크 테슬라 테라팹 공급 계약 뉴스 부각. 패키징 장비 시장 경쟁력 강화 및 우주 섹터 연계 기대. 공매도 세력과의 공방전 예상.</t>
+          <t>나스닥 선물 흐름 및 국내 증시 동향을 고려한 상승 기대감. 외인 매수 동향 주시.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['테라팹', '패키징 장비', '공매도']</t>
+          <t>['나스닥', '선물', '외인매수']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>250000</v>
+        <v>250750</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.40%</t>
+          <t>'+0.70%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1869,10 +1869,10 @@
         <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G16" t="n">
-        <v>1784</v>
+        <v>1758</v>
       </c>
       <c r="H16" t="n">
         <v>46.57</v>
@@ -1898,7 +1898,7 @@
         <v>46.64</v>
       </c>
       <c r="O16" t="n">
-        <v>1128756496250</v>
+        <v>1151417000000</v>
       </c>
       <c r="P16" t="n">
         <v>374500</v>
@@ -1943,83 +1943,83 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14680</v>
+        <v>226000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.14%</t>
+          <t>'+0.44%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-1.17</v>
+        <v>0.15</v>
       </c>
       <c r="E17" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="F17" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="G17" t="n">
-        <v>294</v>
+        <v>719</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>14660</v>
+        <v>225000</v>
       </c>
       <c r="K17" t="n">
-        <v>14980</v>
+        <v>228500</v>
       </c>
       <c r="L17" t="n">
-        <v>15460</v>
+        <v>229000</v>
       </c>
       <c r="M17" t="n">
-        <v>14330</v>
+        <v>219500</v>
       </c>
       <c r="N17" t="n">
-        <v>1.17</v>
+        <v>7.05</v>
       </c>
       <c r="O17" t="n">
-        <v>37685520305</v>
+        <v>67008275750</v>
       </c>
       <c r="P17" t="n">
-        <v>36200</v>
+        <v>426000</v>
       </c>
       <c r="Q17" t="n">
-        <v>8920</v>
+        <v>89500</v>
       </c>
       <c r="R17" t="n">
-        <v>-7000</v>
+        <v>-110000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>이란-미국 관계 완화 및 국제유가 상승 기대감. 후티 반군 공격 및 중국 원유 매집으로 인한 유가 변동성 증폭. 다만, 주가 반응은 미미.</t>
+          <t>머스크 테슬라 '테라팹' 공급 계약 단독 보도 및 기대감. 공매도 세력 관련 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['국제유가', '이란', 'WTI']</t>
+          <t>['테라팹', '공급계약', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,77 +2028,77 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6900</v>
+        <v>10030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.40%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.97</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="F18" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G18" t="n">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>6900</v>
+        <v>9990</v>
       </c>
       <c r="K18" t="n">
-        <v>7500</v>
+        <v>10110</v>
       </c>
       <c r="L18" t="n">
-        <v>8190</v>
+        <v>11390</v>
       </c>
       <c r="M18" t="n">
-        <v>6730</v>
+        <v>9980</v>
       </c>
       <c r="N18" t="n">
-        <v>1.67</v>
+        <v>0.6</v>
       </c>
       <c r="O18" t="n">
-        <v>29440097570</v>
+        <v>144961771400</v>
       </c>
       <c r="P18" t="n">
-        <v>10360</v>
+        <v>15960</v>
       </c>
       <c r="Q18" t="n">
-        <v>2965</v>
+        <v>3500</v>
       </c>
       <c r="R18" t="n">
-        <v>61000</v>
+        <v>21000</v>
       </c>
       <c r="S18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
+          <t>주가 조작 및 공매도 관련 논란, 신약 개발 기대에도 불구하고 하락 압력.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['사이버보안', '양자암호', '공급계약']</t>
+          <t>['주가 조작', '공매도', '신약']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,90 +2120,90 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8790</v>
+        <v>14630</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-0.68%</t>
+          <t>'-0.20%</t>
         </is>
       </c>
       <c r="D19" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="E19" t="n">
+        <v>128</v>
+      </c>
+      <c r="F19" t="n">
+        <v>79</v>
+      </c>
+      <c r="G19" t="n">
+        <v>305</v>
+      </c>
+      <c r="H19" t="n">
         <v>0</v>
       </c>
-      <c r="E19" t="n">
-        <v>86</v>
-      </c>
-      <c r="F19" t="n">
-        <v>48</v>
-      </c>
-      <c r="G19" t="n">
-        <v>287</v>
-      </c>
-      <c r="H19" t="n">
-        <v>27.16</v>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>8850</v>
+        <v>14660</v>
       </c>
       <c r="K19" t="n">
-        <v>8750</v>
+        <v>14980</v>
       </c>
       <c r="L19" t="n">
-        <v>8840</v>
+        <v>15460</v>
       </c>
       <c r="M19" t="n">
-        <v>8670</v>
+        <v>14330</v>
       </c>
       <c r="N19" t="n">
-        <v>27.16</v>
+        <v>1.17</v>
       </c>
       <c r="O19" t="n">
-        <v>14628205690</v>
+        <v>38416014565</v>
       </c>
       <c r="P19" t="n">
-        <v>17950</v>
+        <v>36200</v>
       </c>
       <c r="Q19" t="n">
-        <v>8120</v>
+        <v>8920</v>
       </c>
       <c r="R19" t="n">
-        <v>-290000</v>
+        <v>-7000</v>
       </c>
       <c r="S19" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>하반기 실적 부진 및 목표주가 하향 전망. PBR 기반 저평가 주장과 공매도 이슈 혼재.</t>
+          <t>이란 관련 지정학적 리스크 및 국제 유가 변동성에 따른 단기 등락 전망. 외인 수급 불안정.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['실적 부진', '목표주가', '공매도']</t>
+          <t>['국제유가', '이란', '지정학적리스크']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>86100</v>
+        <v>86600</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-1.03%</t>
+          <t>'-0.46%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.11</v>
       </c>
       <c r="E20" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F20" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G20" t="n">
-        <v>646</v>
+        <v>655</v>
       </c>
       <c r="H20" t="n">
         <v>23.45</v>
@@ -2257,7 +2257,7 @@
         <v>86200</v>
       </c>
       <c r="L20" t="n">
-        <v>86700</v>
+        <v>86800</v>
       </c>
       <c r="M20" t="n">
         <v>85000</v>
@@ -2266,7 +2266,7 @@
         <v>23.56</v>
       </c>
       <c r="O20" t="n">
-        <v>78963379200</v>
+        <v>82474758000</v>
       </c>
       <c r="P20" t="n">
         <v>139200</v>
@@ -2311,83 +2311,83 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14270</v>
+        <v>8790</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-1.52%</t>
+          <t>'-0.68%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F21" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G21" t="n">
-        <v>391</v>
+        <v>290</v>
       </c>
       <c r="H21" t="n">
-        <v>1.8</v>
+        <v>27.16</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>14490</v>
+        <v>8850</v>
       </c>
       <c r="K21" t="n">
-        <v>14410</v>
+        <v>8750</v>
       </c>
       <c r="L21" t="n">
-        <v>14600</v>
+        <v>8840</v>
       </c>
       <c r="M21" t="n">
-        <v>13930</v>
+        <v>8670</v>
       </c>
       <c r="N21" t="n">
-        <v>1.88</v>
+        <v>27.16</v>
       </c>
       <c r="O21" t="n">
-        <v>43869429665</v>
+        <v>14815784210</v>
       </c>
       <c r="P21" t="n">
-        <v>31500</v>
+        <v>17950</v>
       </c>
       <c r="Q21" t="n">
-        <v>1272</v>
+        <v>8120</v>
       </c>
       <c r="R21" t="n">
-        <v>11000</v>
+        <v>-290000</v>
       </c>
       <c r="S21" t="n">
-        <v>-9000</v>
+        <v>-1000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>방송 홍보 효과와 외인 매수 전환에 대한 기대감, 그러나 금리 및 유가 등 거시 경제 변수로 인한 시장 변동성 우려.</t>
+          <t>하반기 실적 부진 및 목표주가 하향 전망. PBR 기반 저평가 주장과 공매도 이슈 혼재.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['외인매수', '대선변수', '금리']</t>
+          <t>['실적 부진', '목표주가', '공매도']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4225</v>
+        <v>14360</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-2.31%</t>
+          <t>'-0.90%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.18</v>
+        <v>-0.08</v>
       </c>
       <c r="E22" t="n">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="F22" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="G22" t="n">
-        <v>158</v>
+        <v>399</v>
       </c>
       <c r="H22" t="n">
-        <v>0.77</v>
+        <v>1.8</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,150 +2435,242 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>4325</v>
+        <v>14490</v>
       </c>
       <c r="K22" t="n">
-        <v>4325</v>
+        <v>14410</v>
       </c>
       <c r="L22" t="n">
-        <v>4415</v>
+        <v>14600</v>
       </c>
       <c r="M22" t="n">
-        <v>4050</v>
+        <v>13930</v>
       </c>
       <c r="N22" t="n">
-        <v>0.59</v>
+        <v>1.88</v>
       </c>
       <c r="O22" t="n">
-        <v>59178590195</v>
+        <v>45464998105</v>
       </c>
       <c r="P22" t="n">
-        <v>8100</v>
+        <v>31500</v>
       </c>
       <c r="Q22" t="n">
-        <v>592</v>
+        <v>1272</v>
       </c>
       <c r="R22" t="n">
-        <v>39000</v>
+        <v>11000</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>삼성SDS와 4381억 공급 계약 체결. 광전자 대비 낮은 상승률 및 매물대 부담.</t>
+          <t>머니투데이 방송 홍보 및 외인 매수 전환에 따른 상승 기대감. 광전자 관련 종목 비교.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['공급 계약', '광전자', '매물대']</t>
+          <t>['홍보', '외인매수', '광통신']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>21100</v>
+        <v>4230</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-4.52%</t>
+          <t>'-2.20%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="E23" t="n">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c r="F23" t="n">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="G23" t="n">
-        <v>308</v>
+        <v>154</v>
       </c>
       <c r="H23" t="n">
-        <v>28.9</v>
+        <v>0.77</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>22100</v>
+        <v>4325</v>
       </c>
       <c r="K23" t="n">
-        <v>21850</v>
+        <v>4325</v>
       </c>
       <c r="L23" t="n">
-        <v>21850</v>
+        <v>4415</v>
       </c>
       <c r="M23" t="n">
-        <v>21000</v>
+        <v>4050</v>
       </c>
       <c r="N23" t="n">
-        <v>28.81</v>
+        <v>0.59</v>
       </c>
       <c r="O23" t="n">
-        <v>41781370525</v>
+        <v>60675240112</v>
       </c>
       <c r="P23" t="n">
-        <v>35350</v>
+        <v>8100</v>
       </c>
       <c r="Q23" t="n">
-        <v>18440</v>
+        <v>592</v>
       </c>
       <c r="R23" t="n">
-        <v>-882000</v>
+        <v>39000</v>
       </c>
       <c r="S23" t="n">
-        <v>-16000</v>
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>12억 달러 규모 수주 공시 확인. 조선업황 회복 기대감 있으나, 시장 반응 및 수급 악화로 인한 주가 하락.</t>
+          <t>삼성SDS와 4381억 공급 계약 체결. 광전자 대비 낮은 상승률 및 매물대 부담.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>['공급 계약', '광전자', '매물대']</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>069540</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>21050</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>'-4.75%</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E24" t="n">
+        <v>130</v>
+      </c>
+      <c r="F24" t="n">
+        <v>76</v>
+      </c>
+      <c r="G24" t="n">
+        <v>312</v>
+      </c>
+      <c r="H24" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>22100</v>
+      </c>
+      <c r="K24" t="n">
+        <v>21850</v>
+      </c>
+      <c r="L24" t="n">
+        <v>21850</v>
+      </c>
+      <c r="M24" t="n">
+        <v>21000</v>
+      </c>
+      <c r="N24" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="O24" t="n">
+        <v>42210378550</v>
+      </c>
+      <c r="P24" t="n">
+        <v>35350</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>18440</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-882000</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-16000</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>12억 달러 규모 수주 공시 확인. 조선업황 회복 기대감 있으나, 시장 반응 및 수급 악화로 인한 주가 하락.</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="n">
         <v>0.5</v>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>['수주 공시', '조선업황', '수급']</t>
         </is>
       </c>
-      <c r="X23" t="n">
+      <c r="X24" t="n">
         <v>2</v>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>010140</t>
         </is>

--- a/data/trending_integrated_20260915_11.xlsx
+++ b/data/trending_integrated_20260915_11.xlsx
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25550</v>
+        <v>25650</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+16.67%</t>
+          <t>'+17.12%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -581,10 +581,10 @@
         <v>60</v>
       </c>
       <c r="F2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G2" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="H2" t="n">
         <v>4.9</v>
@@ -610,7 +610,7 @@
         <v>4.89</v>
       </c>
       <c r="O2" t="n">
-        <v>172146884600</v>
+        <v>175362988200</v>
       </c>
       <c r="P2" t="n">
         <v>50600</v>
@@ -659,18 +659,18 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10610</v>
+        <v>10720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.46%</t>
+          <t>'+15.64%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.06</v>
       </c>
       <c r="E3" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F3" t="n">
         <v>62</v>
@@ -702,7 +702,7 @@
         <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>129426305695</v>
+        <v>130085911540</v>
       </c>
       <c r="P3" t="n">
         <v>25050</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>면역조절 펩타이드 장기지속형 제제 기술 특허 등록 및 관련 기대감. 품절주 특성 언급.</t>
+          <t>장기지속형 주사제 기술 특허 등록 및 노보노디스크 협력 기대감. 품절주 특성 및 높은 목표가 제시.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['특허', '펩타이드', '품절주']</t>
+          <t>['특허', '장기지속형', '품절주']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2855</v>
+        <v>2865</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+10.44%</t>
+          <t>'+10.83%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>1.34</v>
       </c>
       <c r="E4" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F4" t="n">
         <v>44</v>
       </c>
       <c r="G4" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H4" t="n">
         <v>1.34</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>63687918114</v>
+        <v>64257820311</v>
       </c>
       <c r="P4" t="n">
         <v>5100</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35800</v>
+        <v>35550</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.48%</t>
+          <t>'+7.73%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.13</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F5" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G5" t="n">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="H5" t="n">
         <v>14.93</v>
@@ -886,7 +886,7 @@
         <v>15.06</v>
       </c>
       <c r="O5" t="n">
-        <v>40811654875</v>
+        <v>41965305025</v>
       </c>
       <c r="P5" t="n">
         <v>50400</v>
@@ -931,184 +931,184 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51100</v>
+        <v>3640</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.90%</t>
+          <t>'+7.06%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.18</v>
+        <v>0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="F6" t="n">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="G6" t="n">
-        <v>317</v>
+        <v>173</v>
       </c>
       <c r="H6" t="n">
-        <v>13.97</v>
+        <v>0.83</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>47800</v>
+        <v>3400</v>
       </c>
       <c r="K6" t="n">
-        <v>47300</v>
+        <v>3450</v>
       </c>
       <c r="L6" t="n">
-        <v>54600</v>
+        <v>4080</v>
       </c>
       <c r="M6" t="n">
-        <v>46400</v>
+        <v>3445</v>
       </c>
       <c r="N6" t="n">
-        <v>14.15</v>
+        <v>0.71</v>
       </c>
       <c r="O6" t="n">
-        <v>71023318525</v>
+        <v>138114422153</v>
       </c>
       <c r="P6" t="n">
-        <v>108900</v>
+        <v>4335</v>
       </c>
       <c r="Q6" t="n">
-        <v>18230</v>
+        <v>1246</v>
       </c>
       <c r="R6" t="n">
-        <v>89000</v>
+        <v>226000</v>
       </c>
       <c r="S6" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>초대형 계약 체결 가능성 및 수주 성과에 따른 기대감. 외인, 보험, 투신, 연기금 등 기관 매수세 유입 확인.</t>
+          <t>삼익제약과의 경쟁 구도 속에서 주가 변동성. 단기 트레이딩 관점 및 3700원 돌파 여부 주목.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['수주', '계약체결', '기관매수']</t>
+          <t>['단타', '삼익제약', '3700원']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3625</v>
+        <v>51100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.62%</t>
+          <t>'+6.90%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.12</v>
+        <v>-0.18</v>
       </c>
       <c r="E7" t="n">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="F7" t="n">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="G7" t="n">
-        <v>174</v>
+        <v>345</v>
       </c>
       <c r="H7" t="n">
-        <v>0.83</v>
+        <v>13.97</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3400</v>
+        <v>47800</v>
       </c>
       <c r="K7" t="n">
-        <v>3450</v>
+        <v>47300</v>
       </c>
       <c r="L7" t="n">
-        <v>4080</v>
+        <v>54600</v>
       </c>
       <c r="M7" t="n">
-        <v>3445</v>
+        <v>46400</v>
       </c>
       <c r="N7" t="n">
-        <v>0.71</v>
+        <v>14.15</v>
       </c>
       <c r="O7" t="n">
-        <v>137649268614</v>
+        <v>72420142925</v>
       </c>
       <c r="P7" t="n">
-        <v>4335</v>
+        <v>108900</v>
       </c>
       <c r="Q7" t="n">
-        <v>1246</v>
+        <v>18230</v>
       </c>
       <c r="R7" t="n">
-        <v>226000</v>
+        <v>89000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>삼익제약과의 경쟁 구도 속에서 주가 변동성. 단기 트레이딩 관점 및 3700원 돌파 여부 주목.</t>
+          <t>대규모 수주 계약 체결 사실 기반 긍정적 전망. 미국 진출 가속화 및 외인/기관 매수세 유입 확인.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['단타', '삼익제약', '3700원']</t>
+          <t>['수주', '미국진출', '외인매수']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14880</v>
+        <v>14990</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.46%</t>
+          <t>'+6.24%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1136,7 +1136,7 @@
         <v>40</v>
       </c>
       <c r="G8" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H8" t="n">
         <v>10.75</v>
@@ -1162,7 +1162,7 @@
         <v>10.69</v>
       </c>
       <c r="O8" t="n">
-        <v>96839142060</v>
+        <v>97672178905</v>
       </c>
       <c r="P8" t="n">
         <v>23550</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31950</v>
+        <v>31700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.27%</t>
+          <t>'+4.45%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F9" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G9" t="n">
-        <v>599</v>
+        <v>624</v>
       </c>
       <c r="H9" t="n">
         <v>17.5</v>
@@ -1254,7 +1254,7 @@
         <v>17.55</v>
       </c>
       <c r="O9" t="n">
-        <v>10155821975</v>
+        <v>10344317300</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>143200</v>
+        <v>142600</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.75%</t>
+          <t>'+4.32%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G10" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H10" t="n">
         <v>15.81</v>
@@ -1346,7 +1346,7 @@
         <v>15.76</v>
       </c>
       <c r="O10" t="n">
-        <v>87423984400</v>
+        <v>89119602750</v>
       </c>
       <c r="P10" t="n">
         <v>164700</v>
@@ -1391,83 +1391,83 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10710</v>
+        <v>17820</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+4.28%</t>
+          <t>'+3.60%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.26</v>
+        <v>-2.35</v>
       </c>
       <c r="E11" t="n">
-        <v>146</v>
+        <v>97</v>
       </c>
       <c r="F11" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="G11" t="n">
-        <v>355</v>
+        <v>142</v>
       </c>
       <c r="H11" t="n">
-        <v>17.93</v>
+        <v>0.35</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>10270</v>
+        <v>17200</v>
       </c>
       <c r="K11" t="n">
-        <v>11000</v>
+        <v>17220</v>
       </c>
       <c r="L11" t="n">
-        <v>11650</v>
+        <v>18390</v>
       </c>
       <c r="M11" t="n">
-        <v>10010</v>
+        <v>16600</v>
       </c>
       <c r="N11" t="n">
-        <v>17.67</v>
+        <v>2.7</v>
       </c>
       <c r="O11" t="n">
-        <v>309293641455</v>
+        <v>143692880245</v>
       </c>
       <c r="P11" t="n">
-        <v>22450</v>
+        <v>30550</v>
       </c>
       <c r="Q11" t="n">
-        <v>1760</v>
+        <v>6100</v>
       </c>
       <c r="R11" t="n">
-        <v>276000</v>
+        <v>149000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>아이온큐 급등 및 트럼프 AI 발언에 따른 기대감 형성. 다만, 미국 반도체 지수 하락 및 개인 매도 흐름.</t>
+          <t>세계 최초 양자 보안 기술 및 594억 공급 계약 체결 사실 기반 긍정 전망. 미국 보안주 테마.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['아이온큐', 'AI', '반도체']</t>
+          <t>['양자보안', '공급계약', '테마']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17740</v>
+        <v>10620</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.14%</t>
+          <t>'+3.41%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-2.35</v>
+        <v>0.26</v>
       </c>
       <c r="E12" t="n">
-        <v>83</v>
+        <v>147</v>
       </c>
       <c r="F12" t="n">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="G12" t="n">
-        <v>140</v>
+        <v>359</v>
       </c>
       <c r="H12" t="n">
-        <v>0.35</v>
+        <v>17.93</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>17200</v>
+        <v>10270</v>
       </c>
       <c r="K12" t="n">
-        <v>17220</v>
+        <v>11000</v>
       </c>
       <c r="L12" t="n">
-        <v>18390</v>
+        <v>11650</v>
       </c>
       <c r="M12" t="n">
-        <v>16600</v>
+        <v>10010</v>
       </c>
       <c r="N12" t="n">
-        <v>2.7</v>
+        <v>17.67</v>
       </c>
       <c r="O12" t="n">
-        <v>133520180025</v>
+        <v>311772826890</v>
       </c>
       <c r="P12" t="n">
-        <v>30550</v>
+        <v>22450</v>
       </c>
       <c r="Q12" t="n">
-        <v>6100</v>
+        <v>1760</v>
       </c>
       <c r="R12" t="n">
-        <v>149000</v>
+        <v>276000</v>
       </c>
       <c r="S12" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 양자 보안주 폭등 및 세계 최초 기술력 기반 공급 계약 체결 사실. 관련 기업 비교.</t>
+          <t>아이온큐 급등 및 트럼프 AI 발언에 따른 기대감 형성. 다만, 미국 반도체 지수 하락 및 개인 매도 흐름.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['양자보안', '공급계약', '기술력']</t>
+          <t>['아이온큐', 'AI', '반도체']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,77 +1568,77 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19230</v>
+        <v>7060</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.51%</t>
+          <t>'+2.32%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.02</v>
+        <v>-0.97</v>
       </c>
       <c r="E13" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="F13" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="G13" t="n">
-        <v>260</v>
+        <v>102</v>
       </c>
       <c r="H13" t="n">
-        <v>10.53</v>
+        <v>0.7</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>18760</v>
+        <v>6900</v>
       </c>
       <c r="K13" t="n">
-        <v>18440</v>
+        <v>7500</v>
       </c>
       <c r="L13" t="n">
-        <v>19230</v>
+        <v>8190</v>
       </c>
       <c r="M13" t="n">
-        <v>18120</v>
+        <v>6730</v>
       </c>
       <c r="N13" t="n">
-        <v>10.55</v>
+        <v>1.67</v>
       </c>
       <c r="O13" t="n">
-        <v>43754574395</v>
+        <v>31358015775</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>10360</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>2965</v>
       </c>
       <c r="R13" t="n">
-        <v>-67000</v>
+        <v>61000</v>
       </c>
       <c r="S13" t="n">
-        <v>-18000</v>
+        <v>1000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>대차해지 운동 참여 독려 및 건설 대장주로서의 기대감 표출. 해외 건설 수주 가능성 언급.</t>
+          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['대차해지', '해외건설', '건설 대장주']</t>
+          <t>['사이버보안', '양자암호', '공급계약']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,77 +1660,77 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7050</v>
+        <v>19120</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.17%</t>
+          <t>'+1.92%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.97</v>
+        <v>-0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F14" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="G14" t="n">
-        <v>101</v>
+        <v>280</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7</v>
+        <v>10.53</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>6900</v>
+        <v>18760</v>
       </c>
       <c r="K14" t="n">
-        <v>7500</v>
+        <v>18440</v>
       </c>
       <c r="L14" t="n">
-        <v>8190</v>
+        <v>19245</v>
       </c>
       <c r="M14" t="n">
-        <v>6730</v>
+        <v>18120</v>
       </c>
       <c r="N14" t="n">
-        <v>1.67</v>
+        <v>10.55</v>
       </c>
       <c r="O14" t="n">
-        <v>30605731480</v>
+        <v>45872909445</v>
       </c>
       <c r="P14" t="n">
-        <v>10360</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>2965</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>61000</v>
+        <v>-67000</v>
       </c>
       <c r="S14" t="n">
-        <v>1000</v>
+        <v>-18000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
+          <t>대차해지 운동 참여 독려 및 건설 대장주로서의 기대감 표출. 해외 건설 수주 가능성 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['사이버보안', '양자암호', '공급계약']</t>
+          <t>['대차해지', '해외건설', '건설 대장주']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1718000</v>
+        <v>1721000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.24%</t>
+          <t>'+1.41%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="G15" t="n">
-        <v>2099</v>
+        <v>2127</v>
       </c>
       <c r="H15" t="n">
         <v>50.27</v>
@@ -1806,7 +1806,7 @@
         <v>50.47</v>
       </c>
       <c r="O15" t="n">
-        <v>2098326632500</v>
+        <v>2208505268000</v>
       </c>
       <c r="P15" t="n">
         <v>2987000</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>나스닥 선물 흐름 및 국내 증시 동향을 고려한 상승 기대감. 외인 매수 동향 주시.</t>
+          <t>나스닥 선물 흐름 호조에 따른 상승 기대감. 기관 매수세 유입 확인, 조정 끝 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['나스닥', '선물', '외인매수']</t>
+          <t>['나스닥', '기관매수', '조정']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>250750</v>
+        <v>251250</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.70%</t>
+          <t>'+0.90%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1869,10 +1869,10 @@
         <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G16" t="n">
-        <v>1758</v>
+        <v>1765</v>
       </c>
       <c r="H16" t="n">
         <v>46.57</v>
@@ -1898,7 +1898,7 @@
         <v>46.64</v>
       </c>
       <c r="O16" t="n">
-        <v>1151417000000</v>
+        <v>1181475154000</v>
       </c>
       <c r="P16" t="n">
         <v>374500</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>반도체 시장 안정화 및 수요 감소 없음 전망. 저가 매수 기회 언급, 차트 긍정적 분석.</t>
+          <t>시장 회복 기대감 및 메모리 반도체 수요 긍정 전망. 악재 선반영 주장.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['메모리 반도체', '수요', '저가 매수']</t>
+          <t>['시장', '반도체', '기대감']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>226000</v>
+        <v>226500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.44%</t>
+          <t>'+0.67%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.15</v>
       </c>
       <c r="E17" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F17" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G17" t="n">
-        <v>719</v>
+        <v>733</v>
       </c>
       <c r="H17" t="n">
         <v>7.2</v>
@@ -1990,7 +1990,7 @@
         <v>7.05</v>
       </c>
       <c r="O17" t="n">
-        <v>67008275750</v>
+        <v>68281468000</v>
       </c>
       <c r="P17" t="n">
         <v>426000</v>
@@ -2050,13 +2050,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F18" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G18" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="H18" t="n">
         <v>0.6</v>
@@ -2082,7 +2082,7 @@
         <v>0.6</v>
       </c>
       <c r="O18" t="n">
-        <v>144961771400</v>
+        <v>145679128325</v>
       </c>
       <c r="P18" t="n">
         <v>15960</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>주가 조작 및 공매도 관련 논란, 신약 개발 기대에도 불구하고 하락 압력.</t>
+          <t>주가 조작 의혹 및 공매도 관련 부정적 언급 다수. 신약 기대감 언급 있으나 실질적 근거 부족.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가 조작', '공매도', '신약']</t>
+          <t>['주가조작', '공매도', '신약']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14630</v>
+        <v>14640</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-0.20%</t>
+          <t>'-0.14%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-1.17</v>
       </c>
       <c r="E19" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F19" t="n">
         <v>79</v>
       </c>
       <c r="G19" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
         <v>1.17</v>
       </c>
       <c r="O19" t="n">
-        <v>38416014565</v>
+        <v>39004988620</v>
       </c>
       <c r="P19" t="n">
         <v>36200</v>
@@ -2219,31 +2219,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>86600</v>
+        <v>8780</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-0.46%</t>
+          <t>'-0.79%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>156</v>
+        <v>87</v>
       </c>
       <c r="F20" t="n">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G20" t="n">
-        <v>655</v>
+        <v>297</v>
       </c>
       <c r="H20" t="n">
-        <v>23.45</v>
+        <v>27.16</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,51 +2251,51 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>87000</v>
+        <v>8850</v>
       </c>
       <c r="K20" t="n">
-        <v>86200</v>
+        <v>8750</v>
       </c>
       <c r="L20" t="n">
-        <v>86800</v>
+        <v>8840</v>
       </c>
       <c r="M20" t="n">
-        <v>85000</v>
+        <v>8670</v>
       </c>
       <c r="N20" t="n">
-        <v>23.56</v>
+        <v>27.16</v>
       </c>
       <c r="O20" t="n">
-        <v>82474758000</v>
+        <v>15011149070</v>
       </c>
       <c r="P20" t="n">
-        <v>139200</v>
+        <v>17950</v>
       </c>
       <c r="Q20" t="n">
-        <v>57000</v>
+        <v>8120</v>
       </c>
       <c r="R20" t="n">
-        <v>-169000</v>
+        <v>-290000</v>
       </c>
       <c r="S20" t="n">
-        <v>-55000</v>
+        <v>-1000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>원전 사업 및 에너지 독립 기대감과 함께 X에너지 상승 등 긍정적 뉴스가 있으나, 어제 주가 하락에 대한 언급도 있음.</t>
+          <t>하반기 실적 부진 및 목표주가 하향 전망. PBR 기반 저평가 주장과 공매도 이슈 혼재.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['원전', '에너지 독립', 'X에너지']</t>
+          <t>['실적 부진', '목표주가', '공매도']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8790</v>
+        <v>86300</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-0.68%</t>
+          <t>'-0.80%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="E21" t="n">
-        <v>87</v>
+        <v>156</v>
       </c>
       <c r="F21" t="n">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="G21" t="n">
-        <v>290</v>
+        <v>669</v>
       </c>
       <c r="H21" t="n">
-        <v>27.16</v>
+        <v>23.45</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,51 +2343,51 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>8850</v>
+        <v>87000</v>
       </c>
       <c r="K21" t="n">
-        <v>8750</v>
+        <v>86200</v>
       </c>
       <c r="L21" t="n">
-        <v>8840</v>
+        <v>86800</v>
       </c>
       <c r="M21" t="n">
-        <v>8670</v>
+        <v>85000</v>
       </c>
       <c r="N21" t="n">
-        <v>27.16</v>
+        <v>23.56</v>
       </c>
       <c r="O21" t="n">
-        <v>14815784210</v>
+        <v>84873566300</v>
       </c>
       <c r="P21" t="n">
-        <v>17950</v>
+        <v>139200</v>
       </c>
       <c r="Q21" t="n">
-        <v>8120</v>
+        <v>57000</v>
       </c>
       <c r="R21" t="n">
-        <v>-290000</v>
+        <v>-169000</v>
       </c>
       <c r="S21" t="n">
-        <v>-1000</v>
+        <v>-55000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>하반기 실적 부진 및 목표주가 하향 전망. PBR 기반 저평가 주장과 공매도 이슈 혼재.</t>
+          <t>원전 사업 및 에너지 독립 기대감과 함께 X에너지 상승 등 긍정적 뉴스가 있으나, 어제 주가 하락에 대한 언급도 있음.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['실적 부진', '목표주가', '공매도']</t>
+          <t>['원전', '에너지 독립', 'X에너지']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14360</v>
+        <v>14300</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-0.90%</t>
+          <t>'-1.31%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.08</v>
       </c>
       <c r="E22" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F22" t="n">
         <v>57</v>
       </c>
       <c r="G22" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H22" t="n">
         <v>1.8</v>
@@ -2450,7 +2450,7 @@
         <v>1.88</v>
       </c>
       <c r="O22" t="n">
-        <v>45464998105</v>
+        <v>46144399915</v>
       </c>
       <c r="P22" t="n">
         <v>31500</v>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4230</v>
+        <v>4205</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-2.20%</t>
+          <t>'-2.77%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.18</v>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F23" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G23" t="n">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="H23" t="n">
         <v>0.77</v>
@@ -2542,7 +2542,7 @@
         <v>0.59</v>
       </c>
       <c r="O23" t="n">
-        <v>60675240112</v>
+        <v>61333479673</v>
       </c>
       <c r="P23" t="n">
         <v>8100</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>21050</v>
+        <v>21100</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-4.75%</t>
+          <t>'-4.52%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0.09</v>
       </c>
       <c r="E24" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F24" t="n">
         <v>76</v>
       </c>
       <c r="G24" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H24" t="n">
         <v>28.9</v>
@@ -2634,7 +2634,7 @@
         <v>28.81</v>
       </c>
       <c r="O24" t="n">
-        <v>42210378550</v>
+        <v>43528819975</v>
       </c>
       <c r="P24" t="n">
         <v>35350</v>

--- a/data/trending_integrated_20260915_11.xlsx
+++ b/data/trending_integrated_20260915_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25650</v>
+        <v>25400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+17.12%</t>
+          <t>'+15.98%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.01</v>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G2" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="H2" t="n">
         <v>4.9</v>
@@ -610,7 +610,7 @@
         <v>4.89</v>
       </c>
       <c r="O2" t="n">
-        <v>175362988200</v>
+        <v>177333596500</v>
       </c>
       <c r="P2" t="n">
         <v>50600</v>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10720</v>
+        <v>10740</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.64%</t>
+          <t>'+15.86%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -676,7 +676,7 @@
         <v>62</v>
       </c>
       <c r="G3" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="H3" t="n">
         <v>1.19</v>
@@ -702,7 +702,7 @@
         <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>130085911540</v>
+        <v>130574372000</v>
       </c>
       <c r="P3" t="n">
         <v>25050</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>장기지속형 주사제 기술 특허 등록 및 노보노디스크 협력 기대감. 품절주 특성 및 높은 목표가 제시.</t>
+          <t>장기지속형 주사제 기술 특허 등록 및 품절주 부각. 노보노디스크 협력 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['특허', '장기지속형', '품절주']</t>
+          <t>['장기지속형 주사제', '품절주', '특허']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2865</v>
+        <v>2830</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+10.83%</t>
+          <t>'+9.48%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>1.34</v>
       </c>
       <c r="E4" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G4" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H4" t="n">
         <v>1.34</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>64257820311</v>
+        <v>64699655328</v>
       </c>
       <c r="P4" t="n">
         <v>5100</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35550</v>
+        <v>35500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.73%</t>
+          <t>'+7.58%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.13</v>
       </c>
       <c r="E5" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="H5" t="n">
         <v>14.93</v>
@@ -886,7 +886,7 @@
         <v>15.06</v>
       </c>
       <c r="O5" t="n">
-        <v>41965305025</v>
+        <v>42549197850</v>
       </c>
       <c r="P5" t="n">
         <v>50400</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3640</v>
+        <v>3655</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.06%</t>
+          <t>'+7.50%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F6" t="n">
         <v>41</v>
       </c>
       <c r="G6" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H6" t="n">
         <v>0.83</v>
@@ -978,7 +978,7 @@
         <v>0.71</v>
       </c>
       <c r="O6" t="n">
-        <v>138114422153</v>
+        <v>138711884322</v>
       </c>
       <c r="P6" t="n">
         <v>4335</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>51100</v>
+        <v>51200</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.90%</t>
+          <t>'+7.11%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.18</v>
       </c>
       <c r="E7" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F7" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G7" t="n">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="H7" t="n">
         <v>13.97</v>
@@ -1070,7 +1070,7 @@
         <v>14.15</v>
       </c>
       <c r="O7" t="n">
-        <v>72420142925</v>
+        <v>73417695375</v>
       </c>
       <c r="P7" t="n">
         <v>108900</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>대규모 수주 계약 체결 사실 기반 긍정적 전망. 미국 진출 가속화 및 외인/기관 매수세 유입 확인.</t>
+          <t>초대형 수주 계약 체결 및 미국 진출 본격화. 공시 기반 호재 및 수주 관련 기대감.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['수주', '미국진출', '외인매수']</t>
+          <t>['수주', '미국 진출', '수소법']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14990</v>
+        <v>15060</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+6.24%</t>
+          <t>'+6.73%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F8" t="n">
         <v>40</v>
       </c>
       <c r="G8" t="n">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="H8" t="n">
         <v>10.75</v>
@@ -1162,7 +1162,7 @@
         <v>10.69</v>
       </c>
       <c r="O8" t="n">
-        <v>97672178905</v>
+        <v>102364378750</v>
       </c>
       <c r="P8" t="n">
         <v>23550</v>
@@ -1222,13 +1222,13 @@
         <v>-0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F9" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G9" t="n">
-        <v>624</v>
+        <v>643</v>
       </c>
       <c r="H9" t="n">
         <v>17.5</v>
@@ -1254,7 +1254,7 @@
         <v>17.55</v>
       </c>
       <c r="O9" t="n">
-        <v>10344317300</v>
+        <v>10629151850</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>담관암 신약 FDA 허가 기대감 속, 기관 외인 이탈 및 제약 유증 이슈. 승인 확률 85~90% 예측.</t>
+          <t>FDA 승인 관련 기대감 및 부정적 전망 혼재. 담관암 관련 호재 및 유증 영향.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['담관암 신약', 'FDA 허가', '기관 외인 이탈']</t>
+          <t>['FDA 승인', '담관암', '유증']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>142600</v>
+        <v>142200</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.32%</t>
+          <t>'+4.02%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F10" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G10" t="n">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="H10" t="n">
         <v>15.81</v>
@@ -1346,7 +1346,7 @@
         <v>15.76</v>
       </c>
       <c r="O10" t="n">
-        <v>89119602750</v>
+        <v>90420166900</v>
       </c>
       <c r="P10" t="n">
         <v>164700</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>합병 철회 가능성 및 적자 회사 합병 관련 우려 제기. 주주총회 합병 반대 촉구.</t>
+          <t>합병 반대 의견이 다수 제기되었으나, 구체적인 근거나 합병 철회 가능성에 대한 객관적인 정보 부족. 주가 하락에 대한 부정적인 전망이 지배적임.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['합병', '적자', '주주총회']</t>
+          <t>['합병', '반대', '적자']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17820</v>
+        <v>17720</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.60%</t>
+          <t>'+3.02%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-2.35</v>
       </c>
       <c r="E11" t="n">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="F11" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G11" t="n">
-        <v>142</v>
+        <v>185</v>
       </c>
       <c r="H11" t="n">
         <v>0.35</v>
@@ -1438,7 +1438,7 @@
         <v>2.7</v>
       </c>
       <c r="O11" t="n">
-        <v>143692880245</v>
+        <v>149327589710</v>
       </c>
       <c r="P11" t="n">
         <v>30550</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>세계 최초 양자 보안 기술 및 594억 공급 계약 체결 사실 기반 긍정 전망. 미국 보안주 테마.</t>
+          <t>미국 양자 보안주 폭등 및 세계 최초 기술력 언급. 594억 공급 계약 확인.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['양자보안', '공급계약', '테마']</t>
+          <t>['양자 보안', '세계 최초', '공급 계약']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10620</v>
+        <v>10580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.41%</t>
+          <t>'+3.02%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.26</v>
       </c>
       <c r="E12" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F12" t="n">
         <v>99</v>
       </c>
       <c r="G12" t="n">
-        <v>359</v>
+        <v>375</v>
       </c>
       <c r="H12" t="n">
         <v>17.93</v>
@@ -1530,7 +1530,7 @@
         <v>17.67</v>
       </c>
       <c r="O12" t="n">
-        <v>311772826890</v>
+        <v>313357244665</v>
       </c>
       <c r="P12" t="n">
         <v>22450</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>아이온큐 급등 및 트럼프 AI 발언에 따른 기대감 형성. 다만, 미국 반도체 지수 하락 및 개인 매도 흐름.</t>
+          <t>AI 및 트럼프 관련 언급으로 인한 기대감 상승. 미국 시장 흐름 및 기타법인 매수세 확인.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['아이온큐', 'AI', '반도체']</t>
+          <t>['AI', '트럼프', '기타법인']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,70 +1575,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>샌즈랩</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7060</v>
+        <v>19150</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.32%</t>
+          <t>'+2.08%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.97</v>
+        <v>-0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="F13" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="G13" t="n">
-        <v>102</v>
+        <v>288</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7</v>
+        <v>10.53</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>6900</v>
+        <v>18760</v>
       </c>
       <c r="K13" t="n">
-        <v>7500</v>
+        <v>18440</v>
       </c>
       <c r="L13" t="n">
-        <v>8190</v>
+        <v>19245</v>
       </c>
       <c r="M13" t="n">
-        <v>6730</v>
+        <v>18120</v>
       </c>
       <c r="N13" t="n">
-        <v>1.67</v>
+        <v>10.55</v>
       </c>
       <c r="O13" t="n">
-        <v>31358015775</v>
+        <v>46935721305</v>
       </c>
       <c r="P13" t="n">
-        <v>10360</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>2965</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>61000</v>
+        <v>-67000</v>
       </c>
       <c r="S13" t="n">
-        <v>1000</v>
+        <v>-18000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
+          <t>대차해지 운동 참여 독려 및 건설 대장주로서의 기대감 표출. 해외 건설 수주 가능성 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['사이버보안', '양자암호', '공급계약']</t>
+          <t>['대차해지', '해외건설', '건설 대장주']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>411080</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19120</v>
+        <v>1725000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.92%</t>
+          <t>'+1.65%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.02</v>
+        <v>-0.2</v>
       </c>
       <c r="E14" t="n">
-        <v>62</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>39</v>
+        <v>471</v>
       </c>
       <c r="G14" t="n">
-        <v>280</v>
+        <v>2162</v>
       </c>
       <c r="H14" t="n">
-        <v>10.53</v>
+        <v>50.27</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,152 +1699,152 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18760</v>
+        <v>1697000</v>
       </c>
       <c r="K14" t="n">
-        <v>18440</v>
+        <v>1690000</v>
       </c>
       <c r="L14" t="n">
-        <v>19245</v>
+        <v>1727000</v>
       </c>
       <c r="M14" t="n">
-        <v>18120</v>
+        <v>1685000</v>
       </c>
       <c r="N14" t="n">
-        <v>10.55</v>
+        <v>50.47</v>
       </c>
       <c r="O14" t="n">
-        <v>45872909445</v>
+        <v>2290757661000</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>325000</v>
       </c>
       <c r="R14" t="n">
-        <v>-67000</v>
+        <v>-118000</v>
       </c>
       <c r="S14" t="n">
-        <v>-18000</v>
+        <v>-48000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>대차해지 운동 참여 독려 및 건설 대장주로서의 기대감 표출. 해외 건설 수주 가능성 언급.</t>
+          <t>AI 관련 긍정 전망 및 시장 흐름 개선 기대. 외인 매도세 및 기관 매수세 혼재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['대차해지', '해외건설', '건설 대장주']</t>
+          <t>['AI', '시장 흐름', '기관 매수']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>샌즈랩</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1721000</v>
+        <v>7000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.41%</t>
+          <t>'+1.45%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.2</v>
+        <v>-0.97</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>43</v>
       </c>
       <c r="F15" t="n">
-        <v>467</v>
+        <v>28</v>
       </c>
       <c r="G15" t="n">
-        <v>2127</v>
+        <v>111</v>
       </c>
       <c r="H15" t="n">
-        <v>50.27</v>
+        <v>0.7</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1697000</v>
+        <v>6900</v>
       </c>
       <c r="K15" t="n">
-        <v>1690000</v>
+        <v>7500</v>
       </c>
       <c r="L15" t="n">
-        <v>1725000</v>
+        <v>8190</v>
       </c>
       <c r="M15" t="n">
-        <v>1685000</v>
+        <v>6730</v>
       </c>
       <c r="N15" t="n">
-        <v>50.47</v>
+        <v>1.67</v>
       </c>
       <c r="O15" t="n">
-        <v>2208505268000</v>
+        <v>31751027495</v>
       </c>
       <c r="P15" t="n">
-        <v>2987000</v>
+        <v>10360</v>
       </c>
       <c r="Q15" t="n">
-        <v>325000</v>
+        <v>2965</v>
       </c>
       <c r="R15" t="n">
-        <v>-118000</v>
+        <v>61000</v>
       </c>
       <c r="S15" t="n">
-        <v>-48000</v>
+        <v>1000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>나스닥 선물 흐름 호조에 따른 상승 기대감. 기관 매수세 유입 확인, 조정 끝 전망.</t>
+          <t>미국 보안주 강세와 함께 사이버 보안 테마로 엮이며, 미국 기업과 594억 공급계약 및 양자암호 관련 기대감.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['나스닥', '기관매수', '조정']</t>
+          <t>['사이버보안', '양자암호', '공급계약']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>411080</t>
         </is>
       </c>
     </row>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>251250</v>
+        <v>251750</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.90%</t>
+          <t>'+1.10%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1869,10 +1869,10 @@
         <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G16" t="n">
-        <v>1765</v>
+        <v>1739</v>
       </c>
       <c r="H16" t="n">
         <v>46.57</v>
@@ -1898,7 +1898,7 @@
         <v>46.64</v>
       </c>
       <c r="O16" t="n">
-        <v>1181475154000</v>
+        <v>1217102484500</v>
       </c>
       <c r="P16" t="n">
         <v>374500</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>시장 회복 기대감 및 메모리 반도체 수요 긍정 전망. 악재 선반영 주장.</t>
+          <t>시장 안정화 및 메모리 반도체 수요 긍정 전망. 악재 선반영 기대감.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['시장', '반도체', '기대감']</t>
+          <t>['메모리 반도체', '시장 안정화', '악재 선반영']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>226500</v>
+        <v>10060</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.67%</t>
+          <t>'+0.70%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>138</v>
+        <v>85</v>
       </c>
       <c r="F17" t="n">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="G17" t="n">
-        <v>733</v>
+        <v>92</v>
       </c>
       <c r="H17" t="n">
-        <v>7.2</v>
+        <v>0.6</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>225000</v>
+        <v>9990</v>
       </c>
       <c r="K17" t="n">
-        <v>228500</v>
+        <v>10110</v>
       </c>
       <c r="L17" t="n">
-        <v>229000</v>
+        <v>11390</v>
       </c>
       <c r="M17" t="n">
-        <v>219500</v>
+        <v>9980</v>
       </c>
       <c r="N17" t="n">
-        <v>7.05</v>
+        <v>0.6</v>
       </c>
       <c r="O17" t="n">
-        <v>68281468000</v>
+        <v>146019165705</v>
       </c>
       <c r="P17" t="n">
-        <v>426000</v>
+        <v>15960</v>
       </c>
       <c r="Q17" t="n">
-        <v>89500</v>
+        <v>3500</v>
       </c>
       <c r="R17" t="n">
-        <v>-110000</v>
+        <v>21000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>머스크 테슬라 '테라팹' 공급 계약 단독 보도 및 기대감. 공매도 세력 관련 언급.</t>
+          <t>주가 조작 및 공매도 관련 부정적 언급. 신약 관련 기대감 있으나 주가 부진.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['테라팹', '공급계약', '공매도']</t>
+          <t>['주가조작', '공매도', '신약']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10030</v>
+        <v>225500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.40%</t>
+          <t>'+0.22%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E18" t="n">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="F18" t="n">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="G18" t="n">
-        <v>90</v>
+        <v>739</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6</v>
+        <v>7.2</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>9990</v>
+        <v>225000</v>
       </c>
       <c r="K18" t="n">
-        <v>10110</v>
+        <v>228500</v>
       </c>
       <c r="L18" t="n">
-        <v>11390</v>
+        <v>229000</v>
       </c>
       <c r="M18" t="n">
-        <v>9980</v>
+        <v>219500</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6</v>
+        <v>7.05</v>
       </c>
       <c r="O18" t="n">
-        <v>145679128325</v>
+        <v>69321568000</v>
       </c>
       <c r="P18" t="n">
-        <v>15960</v>
+        <v>426000</v>
       </c>
       <c r="Q18" t="n">
-        <v>3500</v>
+        <v>89500</v>
       </c>
       <c r="R18" t="n">
-        <v>21000</v>
+        <v>-110000</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 및 공매도 관련 부정적 언급 다수. 신약 기대감 언급 있으나 실질적 근거 부족.</t>
+          <t>머스크 테슬라 '테라팹' 공급 계약 단독 보도 및 기대감. 공매도 세력 관련 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가조작', '공매도', '신약']</t>
+          <t>['테라팹', '공급계약', '공매도']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>042700</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14640</v>
+        <v>14680</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-0.14%</t>
+          <t>'+0.14%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-1.17</v>
       </c>
       <c r="E19" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F19" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G19" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
         <v>1.17</v>
       </c>
       <c r="O19" t="n">
-        <v>39004988620</v>
+        <v>39258148300</v>
       </c>
       <c r="P19" t="n">
         <v>36200</v>
@@ -2219,31 +2219,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8780</v>
+        <v>86500</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-0.79%</t>
+          <t>'-0.57%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="E20" t="n">
-        <v>87</v>
+        <v>159</v>
       </c>
       <c r="F20" t="n">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G20" t="n">
-        <v>297</v>
+        <v>687</v>
       </c>
       <c r="H20" t="n">
-        <v>27.16</v>
+        <v>23.45</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,51 +2251,51 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>8850</v>
+        <v>87000</v>
       </c>
       <c r="K20" t="n">
-        <v>8750</v>
+        <v>86200</v>
       </c>
       <c r="L20" t="n">
-        <v>8840</v>
+        <v>86800</v>
       </c>
       <c r="M20" t="n">
-        <v>8670</v>
+        <v>85000</v>
       </c>
       <c r="N20" t="n">
-        <v>27.16</v>
+        <v>23.56</v>
       </c>
       <c r="O20" t="n">
-        <v>15011149070</v>
+        <v>86530570100</v>
       </c>
       <c r="P20" t="n">
-        <v>17950</v>
+        <v>139200</v>
       </c>
       <c r="Q20" t="n">
-        <v>8120</v>
+        <v>57000</v>
       </c>
       <c r="R20" t="n">
-        <v>-290000</v>
+        <v>-169000</v>
       </c>
       <c r="S20" t="n">
-        <v>-1000</v>
+        <v>-55000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>하반기 실적 부진 및 목표주가 하향 전망. PBR 기반 저평가 주장과 공매도 이슈 혼재.</t>
+          <t>원전 관련 ETF 출시 및 긍정적인 뉴스 언급. 다만, 단기 급등에 대한 기대감만 존재하며 구체적인 근거는 부족함.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['실적 부진', '목표주가', '공매도']</t>
+          <t>['원전', 'ETF', '추세']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>86300</v>
+        <v>8790</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-0.80%</t>
+          <t>'-0.68%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>156</v>
+        <v>91</v>
       </c>
       <c r="F21" t="n">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="G21" t="n">
-        <v>669</v>
+        <v>304</v>
       </c>
       <c r="H21" t="n">
-        <v>23.45</v>
+        <v>27.16</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,38 +2343,38 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>87000</v>
+        <v>8850</v>
       </c>
       <c r="K21" t="n">
-        <v>86200</v>
+        <v>8750</v>
       </c>
       <c r="L21" t="n">
-        <v>86800</v>
+        <v>8840</v>
       </c>
       <c r="M21" t="n">
-        <v>85000</v>
+        <v>8670</v>
       </c>
       <c r="N21" t="n">
-        <v>23.56</v>
+        <v>27.16</v>
       </c>
       <c r="O21" t="n">
-        <v>84873566300</v>
+        <v>15184743595</v>
       </c>
       <c r="P21" t="n">
-        <v>139200</v>
+        <v>17950</v>
       </c>
       <c r="Q21" t="n">
-        <v>57000</v>
+        <v>8120</v>
       </c>
       <c r="R21" t="n">
-        <v>-169000</v>
+        <v>-290000</v>
       </c>
       <c r="S21" t="n">
-        <v>-55000</v>
+        <v>-1000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>원전 사업 및 에너지 독립 기대감과 함께 X에너지 상승 등 긍정적 뉴스가 있으나, 어제 주가 하락에 대한 언급도 있음.</t>
+          <t>대표이사 사퇴 요구 및 실적 부진 언급. 글로벌 업체 대비 저평가 주장.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', '에너지 독립', 'X에너지']</t>
+          <t>['실적 부진', '저평가', '대표이사']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14300</v>
+        <v>14360</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-1.31%</t>
+          <t>'-0.90%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.08</v>
       </c>
       <c r="E22" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F22" t="n">
         <v>57</v>
       </c>
       <c r="G22" t="n">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="H22" t="n">
         <v>1.8</v>
@@ -2450,7 +2450,7 @@
         <v>1.88</v>
       </c>
       <c r="O22" t="n">
-        <v>46144399915</v>
+        <v>46869367510</v>
       </c>
       <c r="P22" t="n">
         <v>31500</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>머니투데이 방송 홍보 및 외인 매수 전환에 따른 상승 기대감. 광전자 관련 종목 비교.</t>
+          <t>머니투데이 방송에서의 홍보 언급 및 외인 매수 전환 소식이 있으나, AI, FOMC 등 거시 경제 변수에 따른 불확실성 존재. 상승에 대한 기대감은 있으나 명확한 근거는 부족함.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['홍보', '외인매수', '광통신']</t>
+          <t>['광통신', '외인', '변수']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4205</v>
+        <v>4225</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-2.77%</t>
+          <t>'-2.31%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.18</v>
       </c>
       <c r="E23" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F23" t="n">
         <v>38</v>
       </c>
       <c r="G23" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H23" t="n">
         <v>0.77</v>
@@ -2542,7 +2542,7 @@
         <v>0.59</v>
       </c>
       <c r="O23" t="n">
-        <v>61333479673</v>
+        <v>62029403072</v>
       </c>
       <c r="P23" t="n">
         <v>8100</v>
@@ -2602,13 +2602,13 @@
         <v>0.09</v>
       </c>
       <c r="E24" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F24" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G24" t="n">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="H24" t="n">
         <v>28.9</v>
@@ -2634,7 +2634,7 @@
         <v>28.81</v>
       </c>
       <c r="O24" t="n">
-        <v>43528819975</v>
+        <v>44040497925</v>
       </c>
       <c r="P24" t="n">
         <v>35350</v>
@@ -2650,16 +2650,16 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>12억 달러 규모 수주 공시 확인. 조선업황 회복 기대감 있으나, 시장 반응 및 수급 악화로 인한 주가 하락.</t>
+          <t>12억 달러 수주 공시 기반 상승. 수주 규모 대비 주가 반응 및 수급 불안정.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['수주 공시', '조선업황', '수급']</t>
+          <t>['수주 공시', '수급', '조선주']</t>
         </is>
       </c>
       <c r="X24" t="n">
